--- a/docs/Master_Pivot_Framework.xlsx
+++ b/docs/Master_Pivot_Framework.xlsx
@@ -35,29 +35,41 @@
     <definedName name="Itemized_Docs">'Dropdown_Lists'!$F$35:$F$38</definedName>
     <definedName name="Credit_Docs">'Dropdown_Lists'!$G$35:$G$37</definedName>
     <definedName name="Payment_Docs">'Dropdown_Lists'!$H$35:$H$36</definedName>
-    <definedName name="W2_OWNER">'Y2025'!$J$21</definedName>
-    <definedName name="W2_THIRD_PARTY">'Y2025'!$J$22</definedName>
-    <definedName name="W2_TOTAL">'Y2025'!$J$23</definedName>
-    <definedName name="BI_SE_SUBJECT">'Y2025'!$J$24</definedName>
-    <definedName name="BI_ACTIVE_NONSE">'Y2025'!$J$25</definedName>
-    <definedName name="BI_PASSIVE">'Y2025'!$J$26</definedName>
-    <definedName name="TAX_EXEMPT">'Y2025'!$J$27</definedName>
-    <definedName name="QUAL_DIV">'Y2025'!$J$28</definedName>
-    <definedName name="CG_LT">'Y2025'!$J$29</definedName>
-    <definedName name="CG_ST">'Y2025'!$J$30</definedName>
-    <definedName name="SEC1250">'Y2025'!$J$31</definedName>
+    <definedName name="W2_OWNER">'Y2025'!$J$23</definedName>
+    <definedName name="W2_THIRD_PARTY">'Y2025'!$J$24</definedName>
+    <definedName name="W2_TOTAL">'Y2025'!$J$25</definedName>
+    <definedName name="BI_SE_SUBJECT">'Y2025'!$J$26</definedName>
+    <definedName name="BI_ACTIVE_NONSE">'Y2025'!$J$27</definedName>
+    <definedName name="BI_PASSIVE">'Y2025'!$J$28</definedName>
+    <definedName name="TAX_EXEMPT">'Y2025'!$J$29</definedName>
+    <definedName name="QUAL_DIV">'Y2025'!$J$30</definedName>
+    <definedName name="CG_LT">'Y2025'!$J$31</definedName>
+    <definedName name="CG_ST">'Y2025'!$J$32</definedName>
+    <definedName name="SEC1250">'Y2025'!$J$33</definedName>
     <definedName name="Line_1z_Wages">'Y2025'!$M$6</definedName>
-    <definedName name="Line_2b_TaxInt">'Y2025'!$M$7</definedName>
-    <definedName name="Line_3b_OrdDiv">'Y2025'!$M$8</definedName>
-    <definedName name="Line_7_CapGain">'Y2025'!$M$9</definedName>
-    <definedName name="Line_8_OtherInc">'Y2025'!$M$10</definedName>
-    <definedName name="TotalIncome">'Y2025'!$M$11</definedName>
-    <definedName name="AdjToIncome">'Y2025'!$M$12</definedName>
-    <definedName name="AGI">'Y2025'!$M$13</definedName>
-    <definedName name="StdItemDed">'Y2025'!$M$14</definedName>
-    <definedName name="QBI_Deduction">'Y2025'!$M$15</definedName>
-    <definedName name="TaxableIncome">'Y2025'!$M$16</definedName>
-    <definedName name="Drill_Line">'Y2025'!$I$33</definedName>
+    <definedName name="Line_2a_TaxExempt">'Y2025'!$M$7</definedName>
+    <definedName name="Line_2b_TaxInt">'Y2025'!$M$8</definedName>
+    <definedName name="Line_3a_QualDiv">'Y2025'!$M$9</definedName>
+    <definedName name="Line_3b_OrdDiv">'Y2025'!$M$10</definedName>
+    <definedName name="Line_7_CapGain">'Y2025'!$M$11</definedName>
+    <definedName name="Line_8_OtherInc">'Y2025'!$M$12</definedName>
+    <definedName name="TotalIncome">'Y2025'!$M$13</definedName>
+    <definedName name="AdjToIncome">'Y2025'!$M$14</definedName>
+    <definedName name="AGI">'Y2025'!$M$15</definedName>
+    <definedName name="StdItemDed">'Y2025'!$M$16</definedName>
+    <definedName name="QBI_Deduction">'Y2025'!$M$17</definedName>
+    <definedName name="TaxableIncome">'Y2025'!$M$18</definedName>
+    <definedName name="OrdIncome">'Y2025'!$J$37</definedName>
+    <definedName name="MAGI">'Y2025'!$J$38</definedName>
+    <definedName name="NII">'Y2025'!$J$39</definedName>
+    <definedName name="QBI_Income">'Y2025'!$J$40</definedName>
+    <definedName name="TaxableIncome_BeforeQBI">'Y2025'!$J$41</definedName>
+    <definedName name="BusinessLoss">'Y2025'!$J$42</definedName>
+    <definedName name="NetSEIncome">'Y2025'!$J$43</definedName>
+    <definedName name="UBIA">'Y2025'!$J$44</definedName>
+    <definedName name="IsSSTB">'Y2025'!$J$45</definedName>
+    <definedName name="NOL_Carryforward">'Y2025'!$J$46</definedName>
+    <definedName name="Drill_Line">'Y2025'!$I$49</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -866,7 +878,7 @@
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P6" s="4" t="inlineStr">
@@ -1194,7 +1206,7 @@
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P10" s="4" t="inlineStr">
@@ -1570,7 +1582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N47"/>
+  <dimension ref="A1:N63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1735,7 +1747,7 @@
         <v/>
       </c>
       <c r="N6" s="6">
-        <f>HYPERLINK("#Y2025!I33", "↗ drill")</f>
+        <f>HYPERLINK("#Y2025!I49", "↗ drill")</f>
         <v/>
       </c>
     </row>
@@ -1770,29 +1782,28 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2b</t>
+          <t>2a</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Taxable interest</t>
+          <t>Tax-exempt interest (informational — Helper)</t>
         </is>
       </c>
       <c r="J7">
-        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Primary_Line], $H7)</f>
+        <f>TAX_EXEMPT</f>
         <v/>
       </c>
       <c r="K7" s="4" t="n"/>
-      <c r="L7">
-        <f>SUMIFS(tblY2025_Strategies[Amount], tblY2025_Strategies[TargetLine], $H7, tblY2025_Strategies[Status], "Committed") + SUMIFS(tblY2025_Strategies[Amount], tblY2025_Strategies[TargetLine], $H7, tblY2025_Strategies[Status], "Implemented")</f>
-        <v/>
+      <c r="L7" t="n">
+        <v>0</v>
       </c>
       <c r="M7">
-        <f>IF(ISBLANK(K7),J7,K7)+L7</f>
+        <f>IF(ISBLANK(K7),J7,K7)</f>
         <v/>
       </c>
       <c r="N7" s="6">
-        <f>HYPERLINK("#Y2025!I33", "↗ drill")</f>
+        <f>HYPERLINK("#Y2025!I49", "↗ drill")</f>
         <v/>
       </c>
     </row>
@@ -1827,12 +1838,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3b</t>
+          <t>2b</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Ordinary dividends (total — incl qualified)</t>
+          <t>Taxable interest</t>
         </is>
       </c>
       <c r="J8">
@@ -1849,7 +1860,7 @@
         <v/>
       </c>
       <c r="N8" s="6">
-        <f>HYPERLINK("#Y2025!I33", "↗ drill")</f>
+        <f>HYPERLINK("#Y2025!I49", "↗ drill")</f>
         <v/>
       </c>
     </row>
@@ -1884,29 +1895,28 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3a</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Capital gain or (loss)</t>
+          <t>Qualified dividends (informational — Helper)</t>
         </is>
       </c>
       <c r="J9">
-        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Primary_Line], $H9)</f>
+        <f>QUAL_DIV</f>
         <v/>
       </c>
       <c r="K9" s="4" t="n"/>
-      <c r="L9">
-        <f>SUMIFS(tblY2025_Strategies[Amount], tblY2025_Strategies[TargetLine], $H9, tblY2025_Strategies[Status], "Committed") + SUMIFS(tblY2025_Strategies[Amount], tblY2025_Strategies[TargetLine], $H9, tblY2025_Strategies[Status], "Implemented")</f>
-        <v/>
+      <c r="L9" t="n">
+        <v>0</v>
       </c>
       <c r="M9">
-        <f>IF(ISBLANK(K9),J9,K9)+L9</f>
+        <f>IF(ISBLANK(K9),J9,K9)</f>
         <v/>
       </c>
       <c r="N9" s="6">
-        <f>HYPERLINK("#Y2025!I33", "↗ drill")</f>
+        <f>HYPERLINK("#Y2025!I49", "↗ drill")</f>
         <v/>
       </c>
     </row>
@@ -1941,12 +1951,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3b</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Other income (Sch 1)</t>
+          <t>Ordinary dividends (total — incl qualified)</t>
         </is>
       </c>
       <c r="J10">
@@ -1963,19 +1973,19 @@
         <v/>
       </c>
       <c r="N10" s="6">
-        <f>HYPERLINK("#Y2025!I33", "↗ drill")</f>
+        <f>HYPERLINK("#Y2025!I49", "↗ drill")</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="H11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>TOTAL INCOME</t>
+          <t>Capital gain or (loss)</t>
         </is>
       </c>
       <c r="J11">
@@ -1992,19 +2002,19 @@
         <v/>
       </c>
       <c r="N11" s="6">
-        <f>HYPERLINK("#Y2025!I33", "↗ drill")</f>
+        <f>HYPERLINK("#Y2025!I49", "↗ drill")</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="H12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Adjustments to income</t>
+          <t>Other income (incl business income via Sch 1)</t>
         </is>
       </c>
       <c r="J12">
@@ -2021,48 +2031,47 @@
         <v/>
       </c>
       <c r="N12" s="6">
-        <f>HYPERLINK("#Y2025!I33", "↗ drill")</f>
+        <f>HYPERLINK("#Y2025!I49", "↗ drill")</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="H13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AGI</t>
+          <t>TOTAL INCOME</t>
         </is>
       </c>
       <c r="J13">
-        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Primary_Line], $H13)</f>
+        <f>M6+M8+M10+M11+M12</f>
         <v/>
       </c>
       <c r="K13" s="4" t="n"/>
-      <c r="L13">
-        <f>SUMIFS(tblY2025_Strategies[Amount], tblY2025_Strategies[TargetLine], $H13, tblY2025_Strategies[Status], "Committed") + SUMIFS(tblY2025_Strategies[Amount], tblY2025_Strategies[TargetLine], $H13, tblY2025_Strategies[Status], "Implemented")</f>
-        <v/>
+      <c r="L13" t="n">
+        <v>0</v>
       </c>
       <c r="M13">
-        <f>IF(ISBLANK(K13),J13,K13)+L13</f>
+        <f>IF(ISBLANK(K13),J13,K13)</f>
         <v/>
       </c>
       <c r="N13" s="6">
-        <f>HYPERLINK("#Y2025!I33", "↗ drill")</f>
+        <f>HYPERLINK("#Y2025!I49", "↗ drill")</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="H14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Std/Itemized deduction</t>
+          <t>Adjustments to income</t>
         </is>
       </c>
       <c r="J14">
@@ -2079,48 +2088,47 @@
         <v/>
       </c>
       <c r="N14" s="6">
-        <f>HYPERLINK("#Y2025!I33", "↗ drill")</f>
+        <f>HYPERLINK("#Y2025!I49", "↗ drill")</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="H15" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>QBI deduction</t>
+          <t>AGI</t>
         </is>
       </c>
       <c r="J15">
-        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Primary_Line], $H15)</f>
+        <f>M13+M14</f>
         <v/>
       </c>
       <c r="K15" s="4" t="n"/>
-      <c r="L15">
-        <f>SUMIFS(tblY2025_Strategies[Amount], tblY2025_Strategies[TargetLine], $H15, tblY2025_Strategies[Status], "Committed") + SUMIFS(tblY2025_Strategies[Amount], tblY2025_Strategies[TargetLine], $H15, tblY2025_Strategies[Status], "Implemented")</f>
-        <v/>
+      <c r="L15" t="n">
+        <v>0</v>
       </c>
       <c r="M15">
-        <f>IF(ISBLANK(K15),J15,K15)+L15</f>
+        <f>IF(ISBLANK(K15),J15,K15)</f>
         <v/>
       </c>
       <c r="N15" s="6">
-        <f>HYPERLINK("#Y2025!I33", "↗ drill")</f>
+        <f>HYPERLINK("#Y2025!I49", "↗ drill")</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="H16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>TAXABLE INCOME</t>
+          <t>Std/Itemized deduction</t>
         </is>
       </c>
       <c r="J16">
@@ -2137,338 +2145,631 @@
         <v/>
       </c>
       <c r="N16" s="6">
-        <f>HYPERLINK("#Y2025!I33", "↗ drill")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="H19" s="5" t="inlineStr">
+        <f>HYPERLINK("#Y2025!I49", "↗ drill")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>QBI deduction</t>
+        </is>
+      </c>
+      <c r="J17">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Primary_Line], $H17)</f>
+        <v/>
+      </c>
+      <c r="K17" s="4" t="n"/>
+      <c r="L17">
+        <f>SUMIFS(tblY2025_Strategies[Amount], tblY2025_Strategies[TargetLine], $H17, tblY2025_Strategies[Status], "Committed") + SUMIFS(tblY2025_Strategies[Amount], tblY2025_Strategies[TargetLine], $H17, tblY2025_Strategies[Status], "Implemented")</f>
+        <v/>
+      </c>
+      <c r="M17">
+        <f>IF(ISBLANK(K17),J17,K17)+L17</f>
+        <v/>
+      </c>
+      <c r="N17" s="6">
+        <f>HYPERLINK("#Y2025!I49", "↗ drill")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>TAXABLE INCOME</t>
+        </is>
+      </c>
+      <c r="J18">
+        <f>M15+M16+M17</f>
+        <v/>
+      </c>
+      <c r="K18" s="4" t="n"/>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <f>IF(ISBLANK(K18),J18,K18)</f>
+        <v/>
+      </c>
+      <c r="N18" s="6">
+        <f>HYPERLINK("#Y2025!I49", "↗ drill")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>▸ HELPER / TAX-CALC INPUTS — does NOT add to income; reference values for future LAMBDAs</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="H20" s="3" t="inlineStr">
+    <row r="22">
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>Helper Label</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="K20" s="3" t="inlineStr">
+      <c r="K22" s="3" t="inlineStr">
         <is>
           <t>Used by</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>W2_OWNER</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Owner W-2 wages (S-Corp reasonable comp; Treatment_Profile=W2_SCorpOwner)</t>
-        </is>
-      </c>
-      <c r="J21">
-        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Treatment_Profile], "W2_SCorpOwner")</f>
-        <v/>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>FICA_Employer/Employee — True Tax Burden box</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>W2_THIRD_PARTY</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Third-party W-2 wages (Treatment_Profile=W2_Employee)</t>
-        </is>
-      </c>
-      <c r="J22">
-        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Treatment_Profile], "W2_Employee")</f>
-        <v/>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>Calc_SE_Tax (SS-base sharing) · AddlMedicareTax_FN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>W2_TOTAL</t>
+          <t>W2_OWNER</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Total W-2 wages (owner + third-party)</t>
+          <t>Owner W-2 wages (S-Corp reasonable comp; Treatment_Profile=W2_SCorpOwner)</t>
         </is>
       </c>
       <c r="J23">
-        <f>W2_OWNER+W2_THIRD_PARTY</f>
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Treatment_Profile], "W2_SCorpOwner")</f>
         <v/>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Calc_SE_Tax (SS-base sharing) · AddlMedicareTax_FN</t>
+          <t>FICA_Employer/Employee — True Tax Burden box</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>BI_SE_SUBJECT</t>
+          <t>W2_THIRD_PARTY</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Business income subject to SE tax (Sch C, Sch F, active K-1 PTP)</t>
+          <t>Third-party W-2 wages (Treatment_Profile=W2_Employee)</t>
         </is>
       </c>
       <c r="J24">
-        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Bucket], "Business Income", tblMaster_Inputs[SE_Subject], "Yes")</f>
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Treatment_Profile], "W2_Employee")</f>
         <v/>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Calc_SE_Tax base · AddlMedicareTax_FN</t>
+          <t>Calc_SE_Tax (SS-base sharing) · AddlMedicareTax_FN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>BI_ACTIVE_NONSE</t>
+          <t>W2_TOTAL</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Active business income NOT subject to SE (active S-Corp K-1, etc.)</t>
+          <t>Total W-2 wages (owner + third-party)</t>
         </is>
       </c>
       <c r="J25">
-        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Bucket], "Business Income", tblMaster_Inputs[SE_Subject], "No", tblMaster_Inputs[NIIT_Class], "Active")</f>
+        <f>W2_OWNER+W2_THIRD_PARTY</f>
         <v/>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>NIIT exclusion (active) · QBI eligible</t>
+          <t>Calc_SE_Tax (SS-base sharing) · AddlMedicareTax_FN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>BI_PASSIVE</t>
+          <t>BI_SE_SUBJECT</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Passive business income / loss (passive K-1s, Sch E rental)</t>
+          <t>Business income subject to SE tax (Sch C, Sch F, active K-1 PTP)</t>
         </is>
       </c>
       <c r="J26">
-        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Bucket], "Business Income", tblMaster_Inputs[NIIT_Class], "Passive")</f>
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Bucket], "Business Income", tblMaster_Inputs[SE_Subject], "Yes")</f>
         <v/>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>PassiveLossAllowed_FN · NIIT inclusion</t>
+          <t>Calc_SE_Tax base · AddlMedicareTax_FN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>TAX_EXEMPT</t>
+          <t>BI_ACTIVE_NONSE</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Tax-exempt interest (Line 2a; reported but not taxed)</t>
+          <t>Active business income NOT subject to SE (active S-Corp K-1, etc.)</t>
         </is>
       </c>
       <c r="J27">
-        <f>SUMIFS(tblMaster_Inputs[Helper_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Helper_Treatment], "TAX_EXEMPT")</f>
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Bucket], "Business Income", tblMaster_Inputs[SE_Subject], "No", tblMaster_Inputs[NIIT_Class], "Active")</f>
         <v/>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>NIIT_FN (MAGI base)</t>
+          <t>NIIT exclusion (active) · QBI eligible</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>QUAL_DIV</t>
+          <t>BI_PASSIVE</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Qualified dividends (carve-out of Line 3b; LTCG stack)</t>
+          <t>Passive business income / loss (passive K-1s, Sch E rental)</t>
         </is>
       </c>
       <c r="J28">
-        <f>SUMIFS(tblMaster_Inputs[Helper_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Helper_Treatment], "QUAL_DIV")</f>
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Bucket], "Business Income", tblMaster_Inputs[NIIT_Class], "Passive")</f>
         <v/>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Calc_CapGainsTax stacking</t>
+          <t>PassiveLossAllowed_FN · NIIT inclusion</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>CG_LT</t>
+          <t>TAX_EXEMPT</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Long-term capital gains (LT preferential rate; stacks with qualified div)</t>
+          <t>Tax-exempt interest (Line 2a; reported but not taxed)</t>
         </is>
       </c>
       <c r="J29">
-        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Treatment_Profile], "LTCG_Stock") + SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Treatment_Profile], "LTCG_RE") + SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Treatment_Profile], "LTCG_K1_Passthrough") + SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Treatment_Profile], "Sec1250_Recap")</f>
+        <f>SUMIFS(tblMaster_Inputs[Helper_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Helper_Treatment], "TAX_EXEMPT")</f>
         <v/>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Calc_CapGainsTax</t>
+          <t>NIIT_FN (MAGI base)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>CG_ST</t>
+          <t>QUAL_DIV</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Short-term capital gains (taxed as ordinary income)</t>
+          <t>Qualified dividends (carve-out of Line 3b; LTCG stack)</t>
         </is>
       </c>
       <c r="J30">
-        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Treatment_Profile], "STCG_Stock")</f>
+        <f>SUMIFS(tblMaster_Inputs[Helper_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Helper_Treatment], "QUAL_DIV")</f>
         <v/>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Calc_OrdinaryTax (ST folded into ordinary income)</t>
+          <t>Calc_CapGainsTax stacking</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="H31" s="7" t="inlineStr">
         <is>
+          <t>CG_LT</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Long-term capital gains (LT preferential rate; stacks with qualified div)</t>
+        </is>
+      </c>
+      <c r="J31">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Treatment_Profile], "LTCG_Stock") + SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Treatment_Profile], "LTCG_RE") + SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Treatment_Profile], "LTCG_K1_Passthrough") + SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Treatment_Profile], "Sec1250_Recap")</f>
+        <v/>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Calc_CapGainsTax</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>CG_ST</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Short-term capital gains (taxed as ordinary income)</t>
+        </is>
+      </c>
+      <c r="J32">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Treatment_Profile], "STCG_Stock")</f>
+        <v/>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Calc_OrdinaryTax (ST folded into ordinary income)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="H33" s="7" t="inlineStr">
+        <is>
           <t>SEC1250</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>§1250 unrecaptured gain (sub-carve of CG_LT; capped at 25% rate)</t>
         </is>
       </c>
-      <c r="J31">
+      <c r="J33">
         <f>SUMIFS(tblMaster_Inputs[Helper_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Helper_Treatment], "SEC1250")</f>
         <v/>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
         <is>
           <t>Calc_1250Tax</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="H32" s="5" t="inlineStr">
+    <row r="35">
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>▸ TAX CALC INPUTS — derived; each row is a workbook-level named range for LAMBDAs to consume</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Named Range</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>Formula / Value</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>Used by LAMBDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>OrdIncome</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Ordinary income (TaxableIncome - CG_LT - QUAL_DIV - SEC1250)</t>
+        </is>
+      </c>
+      <c r="J37">
+        <f>TaxableIncome-CG_LT-QUAL_DIV-SEC1250</f>
+        <v/>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>Calc_CapGainsTax stacking base · Calc_OrdinaryTax (after carve-outs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>MAGI</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Modified AGI = AGI + tax-exempt interest</t>
+        </is>
+      </c>
+      <c r="J38">
+        <f>AGI+TAX_EXEMPT</f>
+        <v/>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Calc_NIIT · PassiveLossAllowed_FN</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>NII</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Net Investment Income = taxable int + div + cap gain + passive</t>
+        </is>
+      </c>
+      <c r="J39">
+        <f>Line_2b_TaxInt+Line_3b_OrdDiv+Line_7_CapGain+BI_PASSIVE</f>
+        <v/>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>Calc_NIIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>QBI_Income</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>QBI-eligible business income (active business)</t>
+        </is>
+      </c>
+      <c r="J40">
+        <f>BI_SE_SUBJECT+BI_ACTIVE_NONSE</f>
+        <v/>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Calc_QBI_Simple · QBI_FN</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>TaxableIncome_BeforeQBI</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Taxable Income BEFORE QBI deduction (= AGI - StdItemDed)</t>
+        </is>
+      </c>
+      <c r="J41">
+        <f>AGI+StdItemDed</f>
+        <v/>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>Calc_QBI_Simple (cap reference)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>BusinessLoss</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Net business loss (only when negative; for EBL limit)</t>
+        </is>
+      </c>
+      <c r="J42">
+        <f>MIN(0,BI_SE_SUBJECT+BI_ACTIVE_NONSE+BI_PASSIVE)</f>
+        <v/>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>ExcessBusinessLossLimit_FN</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>NetSEIncome</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Net SE income (alias of BI_SE_SUBJECT for LAMBDA clarity)</t>
+        </is>
+      </c>
+      <c r="J43">
+        <f>BI_SE_SUBJECT</f>
+        <v/>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>Calc_SE_Tax · AddlMedicareTax_FN · SETax_FN</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>UBIA</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Unadjusted Basis Immediately After Acquisition (QBI W-2/UBIA test)</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>QBI_FN</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>IsSSTB</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Is Specified Service Trade or Business? (TRUE/FALSE)</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>QBI_FN</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>NOL_Carryforward</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>NOL carryforward available (from prior-year Carryovers; populate manually for now)</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>NOLDeductionAllowed_FN</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="H48" s="5" t="inlineStr">
         <is>
           <t>▸ DRILL DETAIL — pick a line; FILTER below shows the contributing Master_Inputs rows</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="H33" s="8" t="inlineStr">
+    <row r="49">
+      <c r="H49" s="8" t="inlineStr">
         <is>
           <t>Drill into line:</t>
         </is>
       </c>
-      <c r="I33" s="9" t="inlineStr">
+      <c r="I49" s="9" t="inlineStr">
         <is>
           <t>1z</t>
         </is>
       </c>
-      <c r="K33" s="6">
+      <c r="K49" s="6">
         <f>HYPERLINK("#Master_Inputs!A1", "✏ open Master_Inputs to edit")</f>
         <v/>
       </c>
     </row>
-    <row r="35">
-      <c r="H35" s="3" t="inlineStr">
+    <row r="51">
+      <c r="H51" s="3" t="inlineStr">
         <is>
           <t>InputID</t>
         </is>
       </c>
-      <c r="I35" s="3" t="inlineStr">
+      <c r="I51" s="3" t="inlineStr">
         <is>
           <t>Bucket</t>
         </is>
       </c>
-      <c r="J35" s="3" t="inlineStr">
+      <c r="J51" s="3" t="inlineStr">
         <is>
           <t>Treatment_Profile</t>
         </is>
       </c>
-      <c r="K35" s="3" t="inlineStr">
+      <c r="K51" s="3" t="inlineStr">
         <is>
           <t>Payor</t>
         </is>
       </c>
-      <c r="L35" s="3" t="inlineStr">
+      <c r="L51" s="3" t="inlineStr">
         <is>
           <t>Baseline_Amount</t>
         </is>
       </c>
-      <c r="M35" s="3" t="inlineStr">
+      <c r="M51" s="3" t="inlineStr">
         <is>
           <t>Helper_Amount</t>
         </is>
       </c>
-      <c r="N35" s="3" t="inlineStr">
+      <c r="N51" s="3" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="H36">
+    <row r="52">
+      <c r="H52">
         <f>IFERROR(HSTACK(FILTER(tblMaster_Inputs[InputID],          (tblMaster_Inputs[Year]=2025)*(tblMaster_Inputs[Primary_Line]=Drill_Line)),FILTER(tblMaster_Inputs[Bucket],           (tblMaster_Inputs[Year]=2025)*(tblMaster_Inputs[Primary_Line]=Drill_Line)),FILTER(tblMaster_Inputs[Treatment_Profile],(tblMaster_Inputs[Year]=2025)*(tblMaster_Inputs[Primary_Line]=Drill_Line)),FILTER(tblMaster_Inputs[Payor],            (tblMaster_Inputs[Year]=2025)*(tblMaster_Inputs[Primary_Line]=Drill_Line)),FILTER(tblMaster_Inputs[Baseline_Amount],  (tblMaster_Inputs[Year]=2025)*(tblMaster_Inputs[Primary_Line]=Drill_Line)),FILTER(tblMaster_Inputs[Helper_Amount],    (tblMaster_Inputs[Year]=2025)*(tblMaster_Inputs[Primary_Line]=Drill_Line)),FILTER(tblMaster_Inputs[Notes],            (tblMaster_Inputs[Year]=2025)*(tblMaster_Inputs[Primary_Line]=Drill_Line))), "(no rows matching this line / year)")</f>
         <v/>
       </c>
     </row>
-    <row r="47">
-      <c r="H47" s="2" t="inlineStr">
+    <row r="63">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>FILTER output is live — change Drill_Line and the rows update. Use the hyperlink to edit in Master_Inputs.</t>
         </is>
@@ -2482,8 +2783,8 @@
     <dataValidation sqref="E6:E200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Status</formula1>
     </dataValidation>
-    <dataValidation sqref="I33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"1z,2b,3b,7,8,9,10,11,12,13,15"</formula1>
+    <dataValidation sqref="I49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"1z,2a,2b,3a,3b,7,8,9,10,11,12,13,15"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2595,7 +2896,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2642,7 +2943,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2689,7 +2990,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -2736,7 +3037,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2783,7 +3084,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2830,7 +3131,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2877,7 +3178,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2924,7 +3225,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2971,7 +3272,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">

--- a/docs/Master_Pivot_Framework.xlsx
+++ b/docs/Master_Pivot_Framework.xlsx
@@ -8,9 +8,13 @@
   </bookViews>
   <sheets>
     <sheet name="Master_Inputs" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Y2025" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Treatment_Profile_Map" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Dropdown_Lists" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Pivot_Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Pivot_Medium" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Pivot_Detailed" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Pivot_Helpers" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Y2025" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Treatment_Profile_Map" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Dropdown_Lists" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="Bucket">'Dropdown_Lists'!$A$4:$A$11</definedName>
@@ -78,7 +82,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -121,6 +125,10 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00595959"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -157,7 +165,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -165,6 +173,8 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1582,6 +1592,2198 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PIVOT — SUMMARY (most condensed; multi-year baseline from Master_Inputs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Pure baseline aggregation. No overrides, no strategies. Year sheets handle those locally.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1z</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Wages</t>
+        </is>
+      </c>
+      <c r="C5">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2023, tblMaster_Inputs[Primary_Line], "1z")</f>
+        <v/>
+      </c>
+      <c r="D5">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2024, tblMaster_Inputs[Primary_Line], "1z")</f>
+        <v/>
+      </c>
+      <c r="E5">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Primary_Line], "1z")</f>
+        <v/>
+      </c>
+      <c r="F5">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2026, tblMaster_Inputs[Primary_Line], "1z")</f>
+        <v/>
+      </c>
+      <c r="G5">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2027, tblMaster_Inputs[Primary_Line], "1z")</f>
+        <v/>
+      </c>
+      <c r="H5">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2028, tblMaster_Inputs[Primary_Line], "1z")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Interest (taxable, tax-exempt info on Detailed)</t>
+        </is>
+      </c>
+      <c r="C6">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2023, tblMaster_Inputs[Primary_Line], "2b")</f>
+        <v/>
+      </c>
+      <c r="D6">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2024, tblMaster_Inputs[Primary_Line], "2b")</f>
+        <v/>
+      </c>
+      <c r="E6">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Primary_Line], "2b")</f>
+        <v/>
+      </c>
+      <c r="F6">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2026, tblMaster_Inputs[Primary_Line], "2b")</f>
+        <v/>
+      </c>
+      <c r="G6">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2027, tblMaster_Inputs[Primary_Line], "2b")</f>
+        <v/>
+      </c>
+      <c r="H6">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2028, tblMaster_Inputs[Primary_Line], "2b")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dividends (qualified info on Detailed)</t>
+        </is>
+      </c>
+      <c r="C7">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2023, tblMaster_Inputs[Primary_Line], "3b")</f>
+        <v/>
+      </c>
+      <c r="D7">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2024, tblMaster_Inputs[Primary_Line], "3b")</f>
+        <v/>
+      </c>
+      <c r="E7">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Primary_Line], "3b")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2026, tblMaster_Inputs[Primary_Line], "3b")</f>
+        <v/>
+      </c>
+      <c r="G7">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2027, tblMaster_Inputs[Primary_Line], "3b")</f>
+        <v/>
+      </c>
+      <c r="H7">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2028, tblMaster_Inputs[Primary_Line], "3b")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Capital gain or (loss)</t>
+        </is>
+      </c>
+      <c r="C8">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2023, tblMaster_Inputs[Primary_Line], "7")</f>
+        <v/>
+      </c>
+      <c r="D8">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2024, tblMaster_Inputs[Primary_Line], "7")</f>
+        <v/>
+      </c>
+      <c r="E8">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Primary_Line], "7")</f>
+        <v/>
+      </c>
+      <c r="F8">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2026, tblMaster_Inputs[Primary_Line], "7")</f>
+        <v/>
+      </c>
+      <c r="G8">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2027, tblMaster_Inputs[Primary_Line], "7")</f>
+        <v/>
+      </c>
+      <c r="H8">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2028, tblMaster_Inputs[Primary_Line], "7")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Other income (biz total)</t>
+        </is>
+      </c>
+      <c r="C9">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2023, tblMaster_Inputs[Primary_Line], "8")</f>
+        <v/>
+      </c>
+      <c r="D9">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2024, tblMaster_Inputs[Primary_Line], "8")</f>
+        <v/>
+      </c>
+      <c r="E9">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Primary_Line], "8")</f>
+        <v/>
+      </c>
+      <c r="F9">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2026, tblMaster_Inputs[Primary_Line], "8")</f>
+        <v/>
+      </c>
+      <c r="G9">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2027, tblMaster_Inputs[Primary_Line], "8")</f>
+        <v/>
+      </c>
+      <c r="H9">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2028, tblMaster_Inputs[Primary_Line], "8")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="C10" s="5">
+        <f>C5+C6+C7+C8+C9</f>
+        <v/>
+      </c>
+      <c r="D10" s="5">
+        <f>D5+D6+D7+D8+D9</f>
+        <v/>
+      </c>
+      <c r="E10" s="5">
+        <f>E5+E6+E7+E8+E9</f>
+        <v/>
+      </c>
+      <c r="F10" s="5">
+        <f>F5+F6+F7+F8+F9</f>
+        <v/>
+      </c>
+      <c r="G10" s="5">
+        <f>G5+G6+G7+G8+G9</f>
+        <v/>
+      </c>
+      <c r="H10" s="5">
+        <f>H5+H6+H7+H8+H9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Adjustments to income</t>
+        </is>
+      </c>
+      <c r="C11">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2023, tblMaster_Inputs[Primary_Line], "10")</f>
+        <v/>
+      </c>
+      <c r="D11">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2024, tblMaster_Inputs[Primary_Line], "10")</f>
+        <v/>
+      </c>
+      <c r="E11">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Primary_Line], "10")</f>
+        <v/>
+      </c>
+      <c r="F11">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2026, tblMaster_Inputs[Primary_Line], "10")</f>
+        <v/>
+      </c>
+      <c r="G11">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2027, tblMaster_Inputs[Primary_Line], "10")</f>
+        <v/>
+      </c>
+      <c r="H11">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2028, tblMaster_Inputs[Primary_Line], "10")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>AGI</t>
+        </is>
+      </c>
+      <c r="C12" s="5">
+        <f>C10+C11</f>
+        <v/>
+      </c>
+      <c r="D12" s="5">
+        <f>D10+D11</f>
+        <v/>
+      </c>
+      <c r="E12" s="5">
+        <f>E10+E11</f>
+        <v/>
+      </c>
+      <c r="F12" s="5">
+        <f>F10+F11</f>
+        <v/>
+      </c>
+      <c r="G12" s="5">
+        <f>G10+G11</f>
+        <v/>
+      </c>
+      <c r="H12" s="5">
+        <f>H10+H11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Std/Itemized deduction</t>
+        </is>
+      </c>
+      <c r="C13">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2023, tblMaster_Inputs[Primary_Line], "12")</f>
+        <v/>
+      </c>
+      <c r="D13">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2024, tblMaster_Inputs[Primary_Line], "12")</f>
+        <v/>
+      </c>
+      <c r="E13">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Primary_Line], "12")</f>
+        <v/>
+      </c>
+      <c r="F13">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2026, tblMaster_Inputs[Primary_Line], "12")</f>
+        <v/>
+      </c>
+      <c r="G13">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2027, tblMaster_Inputs[Primary_Line], "12")</f>
+        <v/>
+      </c>
+      <c r="H13">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2028, tblMaster_Inputs[Primary_Line], "12")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>QBI deduction</t>
+        </is>
+      </c>
+      <c r="C14">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2023, tblMaster_Inputs[Primary_Line], "13")</f>
+        <v/>
+      </c>
+      <c r="D14">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2024, tblMaster_Inputs[Primary_Line], "13")</f>
+        <v/>
+      </c>
+      <c r="E14">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Primary_Line], "13")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2026, tblMaster_Inputs[Primary_Line], "13")</f>
+        <v/>
+      </c>
+      <c r="G14">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2027, tblMaster_Inputs[Primary_Line], "13")</f>
+        <v/>
+      </c>
+      <c r="H14">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2028, tblMaster_Inputs[Primary_Line], "13")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>TAXABLE INCOME</t>
+        </is>
+      </c>
+      <c r="C15" s="5">
+        <f>C12+C13+C14</f>
+        <v/>
+      </c>
+      <c r="D15" s="5">
+        <f>D12+D13+D14</f>
+        <v/>
+      </c>
+      <c r="E15" s="5">
+        <f>E12+E13+E14</f>
+        <v/>
+      </c>
+      <c r="F15" s="5">
+        <f>F12+F13+F14</f>
+        <v/>
+      </c>
+      <c r="G15" s="5">
+        <f>G12+G13+G14</f>
+        <v/>
+      </c>
+      <c r="H15" s="5">
+        <f>H12+H13+H14</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PIVOT — MEDIUM (biz income broken out by entity type; multi-year baseline)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Same as summary but Line 8 broken into Schedule C / Schedule E rental / Partnership K-1 / S-Corp K-1 / Sch F / Trust K-1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1z</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Wages</t>
+        </is>
+      </c>
+      <c r="C5">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2023, tblMaster_Inputs[Primary_Line], "1z")</f>
+        <v/>
+      </c>
+      <c r="D5">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2024, tblMaster_Inputs[Primary_Line], "1z")</f>
+        <v/>
+      </c>
+      <c r="E5">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Primary_Line], "1z")</f>
+        <v/>
+      </c>
+      <c r="F5">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2026, tblMaster_Inputs[Primary_Line], "1z")</f>
+        <v/>
+      </c>
+      <c r="G5">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2027, tblMaster_Inputs[Primary_Line], "1z")</f>
+        <v/>
+      </c>
+      <c r="H5">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2028, tblMaster_Inputs[Primary_Line], "1z")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Interest</t>
+        </is>
+      </c>
+      <c r="C6">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2023, tblMaster_Inputs[Primary_Line], "2b")</f>
+        <v/>
+      </c>
+      <c r="D6">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2024, tblMaster_Inputs[Primary_Line], "2b")</f>
+        <v/>
+      </c>
+      <c r="E6">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Primary_Line], "2b")</f>
+        <v/>
+      </c>
+      <c r="F6">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2026, tblMaster_Inputs[Primary_Line], "2b")</f>
+        <v/>
+      </c>
+      <c r="G6">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2027, tblMaster_Inputs[Primary_Line], "2b")</f>
+        <v/>
+      </c>
+      <c r="H6">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2028, tblMaster_Inputs[Primary_Line], "2b")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dividends</t>
+        </is>
+      </c>
+      <c r="C7">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2023, tblMaster_Inputs[Primary_Line], "3b")</f>
+        <v/>
+      </c>
+      <c r="D7">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2024, tblMaster_Inputs[Primary_Line], "3b")</f>
+        <v/>
+      </c>
+      <c r="E7">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Primary_Line], "3b")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2026, tblMaster_Inputs[Primary_Line], "3b")</f>
+        <v/>
+      </c>
+      <c r="G7">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2027, tblMaster_Inputs[Primary_Line], "3b")</f>
+        <v/>
+      </c>
+      <c r="H7">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2028, tblMaster_Inputs[Primary_Line], "3b")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Capital gain or (loss)</t>
+        </is>
+      </c>
+      <c r="C8">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2023, tblMaster_Inputs[Primary_Line], "7")</f>
+        <v/>
+      </c>
+      <c r="D8">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2024, tblMaster_Inputs[Primary_Line], "7")</f>
+        <v/>
+      </c>
+      <c r="E8">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Primary_Line], "7")</f>
+        <v/>
+      </c>
+      <c r="F8">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2026, tblMaster_Inputs[Primary_Line], "7")</f>
+        <v/>
+      </c>
+      <c r="G8">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2027, tblMaster_Inputs[Primary_Line], "7")</f>
+        <v/>
+      </c>
+      <c r="H8">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2028, tblMaster_Inputs[Primary_Line], "7")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>8.SchC</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Schedule C</t>
+        </is>
+      </c>
+      <c r="C9">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2023, tblMaster_Inputs[Treatment_Profile], "SchC_Active")</f>
+        <v/>
+      </c>
+      <c r="D9">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2024, tblMaster_Inputs[Treatment_Profile], "SchC_Active")</f>
+        <v/>
+      </c>
+      <c r="E9">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Treatment_Profile], "SchC_Active")</f>
+        <v/>
+      </c>
+      <c r="F9">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2026, tblMaster_Inputs[Treatment_Profile], "SchC_Active")</f>
+        <v/>
+      </c>
+      <c r="G9">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2027, tblMaster_Inputs[Treatment_Profile], "SchC_Active")</f>
+        <v/>
+      </c>
+      <c r="H9">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2028, tblMaster_Inputs[Treatment_Profile], "SchC_Active")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>8.SchE</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Schedule E rental</t>
+        </is>
+      </c>
+      <c r="C10">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2023, tblMaster_Inputs[Bucket], "Business Income", tblMaster_Inputs[NIIT_Class], "Passive")</f>
+        <v/>
+      </c>
+      <c r="D10">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2024, tblMaster_Inputs[Bucket], "Business Income", tblMaster_Inputs[NIIT_Class], "Passive")</f>
+        <v/>
+      </c>
+      <c r="E10">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Bucket], "Business Income", tblMaster_Inputs[NIIT_Class], "Passive")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2026, tblMaster_Inputs[Bucket], "Business Income", tblMaster_Inputs[NIIT_Class], "Passive")</f>
+        <v/>
+      </c>
+      <c r="G10">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2027, tblMaster_Inputs[Bucket], "Business Income", tblMaster_Inputs[NIIT_Class], "Passive")</f>
+        <v/>
+      </c>
+      <c r="H10">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2028, tblMaster_Inputs[Bucket], "Business Income", tblMaster_Inputs[NIIT_Class], "Passive")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>8.PTP</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Partnership K-1 (active+passive)</t>
+        </is>
+      </c>
+      <c r="C11">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2023, tblMaster_Inputs[Treatment_Profile], "K1_PTP_Active") + SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2023, tblMaster_Inputs[Treatment_Profile], "K1_PTP_Passive")</f>
+        <v/>
+      </c>
+      <c r="D11">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2024, tblMaster_Inputs[Treatment_Profile], "K1_PTP_Active") + SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2024, tblMaster_Inputs[Treatment_Profile], "K1_PTP_Passive")</f>
+        <v/>
+      </c>
+      <c r="E11">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Treatment_Profile], "K1_PTP_Active") + SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Treatment_Profile], "K1_PTP_Passive")</f>
+        <v/>
+      </c>
+      <c r="F11">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2026, tblMaster_Inputs[Treatment_Profile], "K1_PTP_Active") + SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2026, tblMaster_Inputs[Treatment_Profile], "K1_PTP_Passive")</f>
+        <v/>
+      </c>
+      <c r="G11">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2027, tblMaster_Inputs[Treatment_Profile], "K1_PTP_Active") + SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2027, tblMaster_Inputs[Treatment_Profile], "K1_PTP_Passive")</f>
+        <v/>
+      </c>
+      <c r="H11">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2028, tblMaster_Inputs[Treatment_Profile], "K1_PTP_Active") + SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2028, tblMaster_Inputs[Treatment_Profile], "K1_PTP_Passive")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>8.SCorp</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>S-Corp K-1 (active+passive)</t>
+        </is>
+      </c>
+      <c r="C12">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2023, tblMaster_Inputs[Treatment_Profile], "K1_SCorp_Active") + SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2023, tblMaster_Inputs[Treatment_Profile], "K1_SCorp_Passive")</f>
+        <v/>
+      </c>
+      <c r="D12">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2024, tblMaster_Inputs[Treatment_Profile], "K1_SCorp_Active") + SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2024, tblMaster_Inputs[Treatment_Profile], "K1_SCorp_Passive")</f>
+        <v/>
+      </c>
+      <c r="E12">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Treatment_Profile], "K1_SCorp_Active") + SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Treatment_Profile], "K1_SCorp_Passive")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2026, tblMaster_Inputs[Treatment_Profile], "K1_SCorp_Active") + SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2026, tblMaster_Inputs[Treatment_Profile], "K1_SCorp_Passive")</f>
+        <v/>
+      </c>
+      <c r="G12">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2027, tblMaster_Inputs[Treatment_Profile], "K1_SCorp_Active") + SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2027, tblMaster_Inputs[Treatment_Profile], "K1_SCorp_Passive")</f>
+        <v/>
+      </c>
+      <c r="H12">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2028, tblMaster_Inputs[Treatment_Profile], "K1_SCorp_Active") + SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2028, tblMaster_Inputs[Treatment_Profile], "K1_SCorp_Passive")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>8.SchF</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Schedule F / farm</t>
+        </is>
+      </c>
+      <c r="C13">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2023, tblMaster_Inputs[Treatment_Profile], "SchF_Active")</f>
+        <v/>
+      </c>
+      <c r="D13">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2024, tblMaster_Inputs[Treatment_Profile], "SchF_Active")</f>
+        <v/>
+      </c>
+      <c r="E13">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Treatment_Profile], "SchF_Active")</f>
+        <v/>
+      </c>
+      <c r="F13">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2026, tblMaster_Inputs[Treatment_Profile], "SchF_Active")</f>
+        <v/>
+      </c>
+      <c r="G13">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2027, tblMaster_Inputs[Treatment_Profile], "SchF_Active")</f>
+        <v/>
+      </c>
+      <c r="H13">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2028, tblMaster_Inputs[Treatment_Profile], "SchF_Active")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>8.Trust</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Trust K-1</t>
+        </is>
+      </c>
+      <c r="C14">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2023, tblMaster_Inputs[Treatment_Profile], "Trust_K1")</f>
+        <v/>
+      </c>
+      <c r="D14">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2024, tblMaster_Inputs[Treatment_Profile], "Trust_K1")</f>
+        <v/>
+      </c>
+      <c r="E14">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Treatment_Profile], "Trust_K1")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2026, tblMaster_Inputs[Treatment_Profile], "Trust_K1")</f>
+        <v/>
+      </c>
+      <c r="G14">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2027, tblMaster_Inputs[Treatment_Profile], "Trust_K1")</f>
+        <v/>
+      </c>
+      <c r="H14">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2028, tblMaster_Inputs[Treatment_Profile], "Trust_K1")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Other income (Line 8 total)</t>
+        </is>
+      </c>
+      <c r="C15" s="5">
+        <f>C9+C10+C11+C12+C13+C14</f>
+        <v/>
+      </c>
+      <c r="D15" s="5">
+        <f>D9+D10+D11+D12+D13+D14</f>
+        <v/>
+      </c>
+      <c r="E15" s="5">
+        <f>E9+E10+E11+E12+E13+E14</f>
+        <v/>
+      </c>
+      <c r="F15" s="5">
+        <f>F9+F10+F11+F12+F13+F14</f>
+        <v/>
+      </c>
+      <c r="G15" s="5">
+        <f>G9+G10+G11+G12+G13+G14</f>
+        <v/>
+      </c>
+      <c r="H15" s="5">
+        <f>H9+H10+H11+H12+H13+H14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="C16" s="5">
+        <f>C5+C6+C7+C8+C15</f>
+        <v/>
+      </c>
+      <c r="D16" s="5">
+        <f>D5+D6+D7+D8+D15</f>
+        <v/>
+      </c>
+      <c r="E16" s="5">
+        <f>E5+E6+E7+E8+E15</f>
+        <v/>
+      </c>
+      <c r="F16" s="5">
+        <f>F5+F6+F7+F8+F15</f>
+        <v/>
+      </c>
+      <c r="G16" s="5">
+        <f>G5+G6+G7+G8+G15</f>
+        <v/>
+      </c>
+      <c r="H16" s="5">
+        <f>H5+H6+H7+H8+H15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Adjustments to income</t>
+        </is>
+      </c>
+      <c r="C17">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2023, tblMaster_Inputs[Primary_Line], "10")</f>
+        <v/>
+      </c>
+      <c r="D17">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2024, tblMaster_Inputs[Primary_Line], "10")</f>
+        <v/>
+      </c>
+      <c r="E17">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Primary_Line], "10")</f>
+        <v/>
+      </c>
+      <c r="F17">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2026, tblMaster_Inputs[Primary_Line], "10")</f>
+        <v/>
+      </c>
+      <c r="G17">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2027, tblMaster_Inputs[Primary_Line], "10")</f>
+        <v/>
+      </c>
+      <c r="H17">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2028, tblMaster_Inputs[Primary_Line], "10")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>AGI</t>
+        </is>
+      </c>
+      <c r="C18" s="5">
+        <f>C16+C17</f>
+        <v/>
+      </c>
+      <c r="D18" s="5">
+        <f>D16+D17</f>
+        <v/>
+      </c>
+      <c r="E18" s="5">
+        <f>E16+E17</f>
+        <v/>
+      </c>
+      <c r="F18" s="5">
+        <f>F16+F17</f>
+        <v/>
+      </c>
+      <c r="G18" s="5">
+        <f>G16+G17</f>
+        <v/>
+      </c>
+      <c r="H18" s="5">
+        <f>H16+H17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Std/Itemized deduction</t>
+        </is>
+      </c>
+      <c r="C19">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2023, tblMaster_Inputs[Primary_Line], "12")</f>
+        <v/>
+      </c>
+      <c r="D19">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2024, tblMaster_Inputs[Primary_Line], "12")</f>
+        <v/>
+      </c>
+      <c r="E19">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Primary_Line], "12")</f>
+        <v/>
+      </c>
+      <c r="F19">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2026, tblMaster_Inputs[Primary_Line], "12")</f>
+        <v/>
+      </c>
+      <c r="G19">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2027, tblMaster_Inputs[Primary_Line], "12")</f>
+        <v/>
+      </c>
+      <c r="H19">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2028, tblMaster_Inputs[Primary_Line], "12")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>QBI deduction</t>
+        </is>
+      </c>
+      <c r="C20">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2023, tblMaster_Inputs[Primary_Line], "13")</f>
+        <v/>
+      </c>
+      <c r="D20">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2024, tblMaster_Inputs[Primary_Line], "13")</f>
+        <v/>
+      </c>
+      <c r="E20">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Primary_Line], "13")</f>
+        <v/>
+      </c>
+      <c r="F20">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2026, tblMaster_Inputs[Primary_Line], "13")</f>
+        <v/>
+      </c>
+      <c r="G20">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2027, tblMaster_Inputs[Primary_Line], "13")</f>
+        <v/>
+      </c>
+      <c r="H20">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2028, tblMaster_Inputs[Primary_Line], "13")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>TAXABLE INCOME</t>
+        </is>
+      </c>
+      <c r="C21" s="5">
+        <f>C18+C19+C20</f>
+        <v/>
+      </c>
+      <c r="D21" s="5">
+        <f>D18+D19+D20</f>
+        <v/>
+      </c>
+      <c r="E21" s="5">
+        <f>E18+E19+E20</f>
+        <v/>
+      </c>
+      <c r="F21" s="5">
+        <f>F18+F19+F20</f>
+        <v/>
+      </c>
+      <c r="G21" s="5">
+        <f>G18+G19+G20</f>
+        <v/>
+      </c>
+      <c r="H21" s="5">
+        <f>H18+H19+H20</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PIVOT — DETAILED (full 1040 page-1 lines incl. informational 2a/3a; multi-year baseline)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2a and 3a are informational (carve-outs of helpers); they don't add to Line 9 Total Income.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1z</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Wages</t>
+        </is>
+      </c>
+      <c r="C5">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2023, tblMaster_Inputs[Primary_Line], "1z")</f>
+        <v/>
+      </c>
+      <c r="D5">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2024, tblMaster_Inputs[Primary_Line], "1z")</f>
+        <v/>
+      </c>
+      <c r="E5">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Primary_Line], "1z")</f>
+        <v/>
+      </c>
+      <c r="F5">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2026, tblMaster_Inputs[Primary_Line], "1z")</f>
+        <v/>
+      </c>
+      <c r="G5">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2027, tblMaster_Inputs[Primary_Line], "1z")</f>
+        <v/>
+      </c>
+      <c r="H5">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2028, tblMaster_Inputs[Primary_Line], "1z")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2a</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Tax-exempt interest (informational)</t>
+        </is>
+      </c>
+      <c r="C6">
+        <f>SUMIFS(tblMaster_Inputs[Helper_Amount], tblMaster_Inputs[Year], 2023, tblMaster_Inputs[Helper_Treatment], "TAX_EXEMPT")</f>
+        <v/>
+      </c>
+      <c r="D6">
+        <f>SUMIFS(tblMaster_Inputs[Helper_Amount], tblMaster_Inputs[Year], 2024, tblMaster_Inputs[Helper_Treatment], "TAX_EXEMPT")</f>
+        <v/>
+      </c>
+      <c r="E6">
+        <f>SUMIFS(tblMaster_Inputs[Helper_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Helper_Treatment], "TAX_EXEMPT")</f>
+        <v/>
+      </c>
+      <c r="F6">
+        <f>SUMIFS(tblMaster_Inputs[Helper_Amount], tblMaster_Inputs[Year], 2026, tblMaster_Inputs[Helper_Treatment], "TAX_EXEMPT")</f>
+        <v/>
+      </c>
+      <c r="G6">
+        <f>SUMIFS(tblMaster_Inputs[Helper_Amount], tblMaster_Inputs[Year], 2027, tblMaster_Inputs[Helper_Treatment], "TAX_EXEMPT")</f>
+        <v/>
+      </c>
+      <c r="H6">
+        <f>SUMIFS(tblMaster_Inputs[Helper_Amount], tblMaster_Inputs[Year], 2028, tblMaster_Inputs[Helper_Treatment], "TAX_EXEMPT")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2b</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Taxable interest</t>
+        </is>
+      </c>
+      <c r="C7">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2023, tblMaster_Inputs[Primary_Line], "2b")</f>
+        <v/>
+      </c>
+      <c r="D7">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2024, tblMaster_Inputs[Primary_Line], "2b")</f>
+        <v/>
+      </c>
+      <c r="E7">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Primary_Line], "2b")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2026, tblMaster_Inputs[Primary_Line], "2b")</f>
+        <v/>
+      </c>
+      <c r="G7">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2027, tblMaster_Inputs[Primary_Line], "2b")</f>
+        <v/>
+      </c>
+      <c r="H7">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2028, tblMaster_Inputs[Primary_Line], "2b")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>3a</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Qualified dividends (informational)</t>
+        </is>
+      </c>
+      <c r="C8">
+        <f>SUMIFS(tblMaster_Inputs[Helper_Amount], tblMaster_Inputs[Year], 2023, tblMaster_Inputs[Helper_Treatment], "QUAL_DIV")</f>
+        <v/>
+      </c>
+      <c r="D8">
+        <f>SUMIFS(tblMaster_Inputs[Helper_Amount], tblMaster_Inputs[Year], 2024, tblMaster_Inputs[Helper_Treatment], "QUAL_DIV")</f>
+        <v/>
+      </c>
+      <c r="E8">
+        <f>SUMIFS(tblMaster_Inputs[Helper_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Helper_Treatment], "QUAL_DIV")</f>
+        <v/>
+      </c>
+      <c r="F8">
+        <f>SUMIFS(tblMaster_Inputs[Helper_Amount], tblMaster_Inputs[Year], 2026, tblMaster_Inputs[Helper_Treatment], "QUAL_DIV")</f>
+        <v/>
+      </c>
+      <c r="G8">
+        <f>SUMIFS(tblMaster_Inputs[Helper_Amount], tblMaster_Inputs[Year], 2027, tblMaster_Inputs[Helper_Treatment], "QUAL_DIV")</f>
+        <v/>
+      </c>
+      <c r="H8">
+        <f>SUMIFS(tblMaster_Inputs[Helper_Amount], tblMaster_Inputs[Year], 2028, tblMaster_Inputs[Helper_Treatment], "QUAL_DIV")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3b</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ordinary dividends (total incl qualified)</t>
+        </is>
+      </c>
+      <c r="C9">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2023, tblMaster_Inputs[Primary_Line], "3b")</f>
+        <v/>
+      </c>
+      <c r="D9">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2024, tblMaster_Inputs[Primary_Line], "3b")</f>
+        <v/>
+      </c>
+      <c r="E9">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Primary_Line], "3b")</f>
+        <v/>
+      </c>
+      <c r="F9">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2026, tblMaster_Inputs[Primary_Line], "3b")</f>
+        <v/>
+      </c>
+      <c r="G9">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2027, tblMaster_Inputs[Primary_Line], "3b")</f>
+        <v/>
+      </c>
+      <c r="H9">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2028, tblMaster_Inputs[Primary_Line], "3b")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Capital gain or (loss)</t>
+        </is>
+      </c>
+      <c r="C10">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2023, tblMaster_Inputs[Primary_Line], "7")</f>
+        <v/>
+      </c>
+      <c r="D10">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2024, tblMaster_Inputs[Primary_Line], "7")</f>
+        <v/>
+      </c>
+      <c r="E10">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Primary_Line], "7")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2026, tblMaster_Inputs[Primary_Line], "7")</f>
+        <v/>
+      </c>
+      <c r="G10">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2027, tblMaster_Inputs[Primary_Line], "7")</f>
+        <v/>
+      </c>
+      <c r="H10">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2028, tblMaster_Inputs[Primary_Line], "7")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Other income (biz via Sch 1)</t>
+        </is>
+      </c>
+      <c r="C11">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2023, tblMaster_Inputs[Primary_Line], "8")</f>
+        <v/>
+      </c>
+      <c r="D11">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2024, tblMaster_Inputs[Primary_Line], "8")</f>
+        <v/>
+      </c>
+      <c r="E11">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Primary_Line], "8")</f>
+        <v/>
+      </c>
+      <c r="F11">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2026, tblMaster_Inputs[Primary_Line], "8")</f>
+        <v/>
+      </c>
+      <c r="G11">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2027, tblMaster_Inputs[Primary_Line], "8")</f>
+        <v/>
+      </c>
+      <c r="H11">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2028, tblMaster_Inputs[Primary_Line], "8")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="C12" s="5">
+        <f>C5+C7+C9+C10+C11</f>
+        <v/>
+      </c>
+      <c r="D12" s="5">
+        <f>D5+D7+D9+D10+D11</f>
+        <v/>
+      </c>
+      <c r="E12" s="5">
+        <f>E5+E7+E9+E10+E11</f>
+        <v/>
+      </c>
+      <c r="F12" s="5">
+        <f>F5+F7+F9+F10+F11</f>
+        <v/>
+      </c>
+      <c r="G12" s="5">
+        <f>G5+G7+G9+G10+G11</f>
+        <v/>
+      </c>
+      <c r="H12" s="5">
+        <f>H5+H7+H9+H10+H11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Adjustments to income</t>
+        </is>
+      </c>
+      <c r="C13">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2023, tblMaster_Inputs[Primary_Line], "10")</f>
+        <v/>
+      </c>
+      <c r="D13">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2024, tblMaster_Inputs[Primary_Line], "10")</f>
+        <v/>
+      </c>
+      <c r="E13">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Primary_Line], "10")</f>
+        <v/>
+      </c>
+      <c r="F13">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2026, tblMaster_Inputs[Primary_Line], "10")</f>
+        <v/>
+      </c>
+      <c r="G13">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2027, tblMaster_Inputs[Primary_Line], "10")</f>
+        <v/>
+      </c>
+      <c r="H13">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2028, tblMaster_Inputs[Primary_Line], "10")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>AGI</t>
+        </is>
+      </c>
+      <c r="C14" s="5">
+        <f>C12+C13</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>D12+D13</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>E12+E13</f>
+        <v/>
+      </c>
+      <c r="F14" s="5">
+        <f>F12+F13</f>
+        <v/>
+      </c>
+      <c r="G14" s="5">
+        <f>G12+G13</f>
+        <v/>
+      </c>
+      <c r="H14" s="5">
+        <f>H12+H13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Std/Itemized deduction</t>
+        </is>
+      </c>
+      <c r="C15">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2023, tblMaster_Inputs[Primary_Line], "12")</f>
+        <v/>
+      </c>
+      <c r="D15">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2024, tblMaster_Inputs[Primary_Line], "12")</f>
+        <v/>
+      </c>
+      <c r="E15">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Primary_Line], "12")</f>
+        <v/>
+      </c>
+      <c r="F15">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2026, tblMaster_Inputs[Primary_Line], "12")</f>
+        <v/>
+      </c>
+      <c r="G15">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2027, tblMaster_Inputs[Primary_Line], "12")</f>
+        <v/>
+      </c>
+      <c r="H15">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2028, tblMaster_Inputs[Primary_Line], "12")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>QBI deduction</t>
+        </is>
+      </c>
+      <c r="C16">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2023, tblMaster_Inputs[Primary_Line], "13")</f>
+        <v/>
+      </c>
+      <c r="D16">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2024, tblMaster_Inputs[Primary_Line], "13")</f>
+        <v/>
+      </c>
+      <c r="E16">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Primary_Line], "13")</f>
+        <v/>
+      </c>
+      <c r="F16">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2026, tblMaster_Inputs[Primary_Line], "13")</f>
+        <v/>
+      </c>
+      <c r="G16">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2027, tblMaster_Inputs[Primary_Line], "13")</f>
+        <v/>
+      </c>
+      <c r="H16">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2028, tblMaster_Inputs[Primary_Line], "13")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>TAXABLE INCOME</t>
+        </is>
+      </c>
+      <c r="C17" s="5">
+        <f>C14+C15+C16</f>
+        <v/>
+      </c>
+      <c r="D17" s="5">
+        <f>D14+D15+D16</f>
+        <v/>
+      </c>
+      <c r="E17" s="5">
+        <f>E14+E15+E16</f>
+        <v/>
+      </c>
+      <c r="F17" s="5">
+        <f>F14+F15+F16</f>
+        <v/>
+      </c>
+      <c r="G17" s="5">
+        <f>G14+G15+G16</f>
+        <v/>
+      </c>
+      <c r="H17" s="5">
+        <f>H14+H15+H16</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PIVOT — HELPERS / TAX-CALC INPUTS (multi-year; sub-carves of main pivot lines; do NOT add to 1040 totals)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>These exist for LAMBDA inputs only — qualified div for LTCG stacking, owner W-2 for FICA, etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>W2_OWNER</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Owner W-2 wages (Treatment_Profile=W2_SCorpOwner)</t>
+        </is>
+      </c>
+      <c r="C5">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2023, tblMaster_Inputs[Treatment_Profile], "W2_SCorpOwner")</f>
+        <v/>
+      </c>
+      <c r="D5">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2024, tblMaster_Inputs[Treatment_Profile], "W2_SCorpOwner")</f>
+        <v/>
+      </c>
+      <c r="E5">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Treatment_Profile], "W2_SCorpOwner")</f>
+        <v/>
+      </c>
+      <c r="F5">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2026, tblMaster_Inputs[Treatment_Profile], "W2_SCorpOwner")</f>
+        <v/>
+      </c>
+      <c r="G5">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2027, tblMaster_Inputs[Treatment_Profile], "W2_SCorpOwner")</f>
+        <v/>
+      </c>
+      <c r="H5">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2028, tblMaster_Inputs[Treatment_Profile], "W2_SCorpOwner")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>W2_THIRD_PARTY</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Third-party W-2 wages (Treatment_Profile=W2_Employee)</t>
+        </is>
+      </c>
+      <c r="C6">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2023, tblMaster_Inputs[Treatment_Profile], "W2_Employee")</f>
+        <v/>
+      </c>
+      <c r="D6">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2024, tblMaster_Inputs[Treatment_Profile], "W2_Employee")</f>
+        <v/>
+      </c>
+      <c r="E6">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Treatment_Profile], "W2_Employee")</f>
+        <v/>
+      </c>
+      <c r="F6">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2026, tblMaster_Inputs[Treatment_Profile], "W2_Employee")</f>
+        <v/>
+      </c>
+      <c r="G6">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2027, tblMaster_Inputs[Treatment_Profile], "W2_Employee")</f>
+        <v/>
+      </c>
+      <c r="H6">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2028, tblMaster_Inputs[Treatment_Profile], "W2_Employee")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>W2_TOTAL</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Total W-2 (owner + third-party)</t>
+        </is>
+      </c>
+      <c r="C7" s="5">
+        <f>C5+C6</f>
+        <v/>
+      </c>
+      <c r="D7" s="5">
+        <f>D5+D6</f>
+        <v/>
+      </c>
+      <c r="E7" s="5">
+        <f>E5+E6</f>
+        <v/>
+      </c>
+      <c r="F7" s="5">
+        <f>F5+F6</f>
+        <v/>
+      </c>
+      <c r="G7" s="5">
+        <f>G5+G6</f>
+        <v/>
+      </c>
+      <c r="H7" s="5">
+        <f>H5+H6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BI_SE_SUBJECT</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Biz income subject to SE (Sch C/F + active K-1 PTP)</t>
+        </is>
+      </c>
+      <c r="C8">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2023, tblMaster_Inputs[Bucket], "Business Income", tblMaster_Inputs[SE_Subject], "Yes")</f>
+        <v/>
+      </c>
+      <c r="D8">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2024, tblMaster_Inputs[Bucket], "Business Income", tblMaster_Inputs[SE_Subject], "Yes")</f>
+        <v/>
+      </c>
+      <c r="E8">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Bucket], "Business Income", tblMaster_Inputs[SE_Subject], "Yes")</f>
+        <v/>
+      </c>
+      <c r="F8">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2026, tblMaster_Inputs[Bucket], "Business Income", tblMaster_Inputs[SE_Subject], "Yes")</f>
+        <v/>
+      </c>
+      <c r="G8">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2027, tblMaster_Inputs[Bucket], "Business Income", tblMaster_Inputs[SE_Subject], "Yes")</f>
+        <v/>
+      </c>
+      <c r="H8">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2028, tblMaster_Inputs[Bucket], "Business Income", tblMaster_Inputs[SE_Subject], "Yes")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BI_ACTIVE_NONSE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Active biz income NOT subject to SE</t>
+        </is>
+      </c>
+      <c r="C9">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2023, tblMaster_Inputs[Bucket], "Business Income", tblMaster_Inputs[SE_Subject], "No", tblMaster_Inputs[NIIT_Class], "Active")</f>
+        <v/>
+      </c>
+      <c r="D9">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2024, tblMaster_Inputs[Bucket], "Business Income", tblMaster_Inputs[SE_Subject], "No", tblMaster_Inputs[NIIT_Class], "Active")</f>
+        <v/>
+      </c>
+      <c r="E9">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Bucket], "Business Income", tblMaster_Inputs[SE_Subject], "No", tblMaster_Inputs[NIIT_Class], "Active")</f>
+        <v/>
+      </c>
+      <c r="F9">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2026, tblMaster_Inputs[Bucket], "Business Income", tblMaster_Inputs[SE_Subject], "No", tblMaster_Inputs[NIIT_Class], "Active")</f>
+        <v/>
+      </c>
+      <c r="G9">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2027, tblMaster_Inputs[Bucket], "Business Income", tblMaster_Inputs[SE_Subject], "No", tblMaster_Inputs[NIIT_Class], "Active")</f>
+        <v/>
+      </c>
+      <c r="H9">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2028, tblMaster_Inputs[Bucket], "Business Income", tblMaster_Inputs[SE_Subject], "No", tblMaster_Inputs[NIIT_Class], "Active")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BI_PASSIVE</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Passive biz income (passive K-1s, Sch E)</t>
+        </is>
+      </c>
+      <c r="C10">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2023, tblMaster_Inputs[Bucket], "Business Income", tblMaster_Inputs[NIIT_Class], "Passive")</f>
+        <v/>
+      </c>
+      <c r="D10">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2024, tblMaster_Inputs[Bucket], "Business Income", tblMaster_Inputs[NIIT_Class], "Passive")</f>
+        <v/>
+      </c>
+      <c r="E10">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Bucket], "Business Income", tblMaster_Inputs[NIIT_Class], "Passive")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2026, tblMaster_Inputs[Bucket], "Business Income", tblMaster_Inputs[NIIT_Class], "Passive")</f>
+        <v/>
+      </c>
+      <c r="G10">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2027, tblMaster_Inputs[Bucket], "Business Income", tblMaster_Inputs[NIIT_Class], "Passive")</f>
+        <v/>
+      </c>
+      <c r="H10">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2028, tblMaster_Inputs[Bucket], "Business Income", tblMaster_Inputs[NIIT_Class], "Passive")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TAX_EXEMPT</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Tax-exempt interest (informational; Line 2a)</t>
+        </is>
+      </c>
+      <c r="C11">
+        <f>SUMIFS(tblMaster_Inputs[Helper_Amount], tblMaster_Inputs[Year], 2023, tblMaster_Inputs[Helper_Treatment], "TAX_EXEMPT")</f>
+        <v/>
+      </c>
+      <c r="D11">
+        <f>SUMIFS(tblMaster_Inputs[Helper_Amount], tblMaster_Inputs[Year], 2024, tblMaster_Inputs[Helper_Treatment], "TAX_EXEMPT")</f>
+        <v/>
+      </c>
+      <c r="E11">
+        <f>SUMIFS(tblMaster_Inputs[Helper_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Helper_Treatment], "TAX_EXEMPT")</f>
+        <v/>
+      </c>
+      <c r="F11">
+        <f>SUMIFS(tblMaster_Inputs[Helper_Amount], tblMaster_Inputs[Year], 2026, tblMaster_Inputs[Helper_Treatment], "TAX_EXEMPT")</f>
+        <v/>
+      </c>
+      <c r="G11">
+        <f>SUMIFS(tblMaster_Inputs[Helper_Amount], tblMaster_Inputs[Year], 2027, tblMaster_Inputs[Helper_Treatment], "TAX_EXEMPT")</f>
+        <v/>
+      </c>
+      <c r="H11">
+        <f>SUMIFS(tblMaster_Inputs[Helper_Amount], tblMaster_Inputs[Year], 2028, tblMaster_Inputs[Helper_Treatment], "TAX_EXEMPT")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>QUAL_DIV</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Qualified dividends (carve of 3b; LTCG stack)</t>
+        </is>
+      </c>
+      <c r="C12">
+        <f>SUMIFS(tblMaster_Inputs[Helper_Amount], tblMaster_Inputs[Year], 2023, tblMaster_Inputs[Helper_Treatment], "QUAL_DIV")</f>
+        <v/>
+      </c>
+      <c r="D12">
+        <f>SUMIFS(tblMaster_Inputs[Helper_Amount], tblMaster_Inputs[Year], 2024, tblMaster_Inputs[Helper_Treatment], "QUAL_DIV")</f>
+        <v/>
+      </c>
+      <c r="E12">
+        <f>SUMIFS(tblMaster_Inputs[Helper_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Helper_Treatment], "QUAL_DIV")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f>SUMIFS(tblMaster_Inputs[Helper_Amount], tblMaster_Inputs[Year], 2026, tblMaster_Inputs[Helper_Treatment], "QUAL_DIV")</f>
+        <v/>
+      </c>
+      <c r="G12">
+        <f>SUMIFS(tblMaster_Inputs[Helper_Amount], tblMaster_Inputs[Year], 2027, tblMaster_Inputs[Helper_Treatment], "QUAL_DIV")</f>
+        <v/>
+      </c>
+      <c r="H12">
+        <f>SUMIFS(tblMaster_Inputs[Helper_Amount], tblMaster_Inputs[Year], 2028, tblMaster_Inputs[Helper_Treatment], "QUAL_DIV")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CG_LT</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Long-term cap gains (LTCG_Stock + LTCG_RE + LTCG_K1_Passthrough + Sec1250_Recap)</t>
+        </is>
+      </c>
+      <c r="C13">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2023, tblMaster_Inputs[Treatment_Profile], "LTCG_Stock") + SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2023, tblMaster_Inputs[Treatment_Profile], "LTCG_RE") + SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2023, tblMaster_Inputs[Treatment_Profile], "LTCG_K1_Passthrough") + SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2023, tblMaster_Inputs[Treatment_Profile], "Sec1250_Recap")</f>
+        <v/>
+      </c>
+      <c r="D13">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2024, tblMaster_Inputs[Treatment_Profile], "LTCG_Stock") + SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2024, tblMaster_Inputs[Treatment_Profile], "LTCG_RE") + SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2024, tblMaster_Inputs[Treatment_Profile], "LTCG_K1_Passthrough") + SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2024, tblMaster_Inputs[Treatment_Profile], "Sec1250_Recap")</f>
+        <v/>
+      </c>
+      <c r="E13">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Treatment_Profile], "LTCG_Stock") + SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Treatment_Profile], "LTCG_RE") + SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Treatment_Profile], "LTCG_K1_Passthrough") + SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Treatment_Profile], "Sec1250_Recap")</f>
+        <v/>
+      </c>
+      <c r="F13">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2026, tblMaster_Inputs[Treatment_Profile], "LTCG_Stock") + SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2026, tblMaster_Inputs[Treatment_Profile], "LTCG_RE") + SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2026, tblMaster_Inputs[Treatment_Profile], "LTCG_K1_Passthrough") + SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2026, tblMaster_Inputs[Treatment_Profile], "Sec1250_Recap")</f>
+        <v/>
+      </c>
+      <c r="G13">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2027, tblMaster_Inputs[Treatment_Profile], "LTCG_Stock") + SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2027, tblMaster_Inputs[Treatment_Profile], "LTCG_RE") + SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2027, tblMaster_Inputs[Treatment_Profile], "LTCG_K1_Passthrough") + SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2027, tblMaster_Inputs[Treatment_Profile], "Sec1250_Recap")</f>
+        <v/>
+      </c>
+      <c r="H13">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2028, tblMaster_Inputs[Treatment_Profile], "LTCG_Stock") + SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2028, tblMaster_Inputs[Treatment_Profile], "LTCG_RE") + SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2028, tblMaster_Inputs[Treatment_Profile], "LTCG_K1_Passthrough") + SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2028, tblMaster_Inputs[Treatment_Profile], "Sec1250_Recap")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CG_ST</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Short-term cap gains (STCG_Stock)</t>
+        </is>
+      </c>
+      <c r="C14">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2023, tblMaster_Inputs[Treatment_Profile], "STCG_Stock")</f>
+        <v/>
+      </c>
+      <c r="D14">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2024, tblMaster_Inputs[Treatment_Profile], "STCG_Stock")</f>
+        <v/>
+      </c>
+      <c r="E14">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Treatment_Profile], "STCG_Stock")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2026, tblMaster_Inputs[Treatment_Profile], "STCG_Stock")</f>
+        <v/>
+      </c>
+      <c r="G14">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2027, tblMaster_Inputs[Treatment_Profile], "STCG_Stock")</f>
+        <v/>
+      </c>
+      <c r="H14">
+        <f>SUMIFS(tblMaster_Inputs[Baseline_Amount], tblMaster_Inputs[Year], 2028, tblMaster_Inputs[Treatment_Profile], "STCG_Stock")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SEC1250</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>§1250 unrecaptured (sub-carve of CG_LT; 25% cap)</t>
+        </is>
+      </c>
+      <c r="C15">
+        <f>SUMIFS(tblMaster_Inputs[Helper_Amount], tblMaster_Inputs[Year], 2023, tblMaster_Inputs[Helper_Treatment], "SEC1250")</f>
+        <v/>
+      </c>
+      <c r="D15">
+        <f>SUMIFS(tblMaster_Inputs[Helper_Amount], tblMaster_Inputs[Year], 2024, tblMaster_Inputs[Helper_Treatment], "SEC1250")</f>
+        <v/>
+      </c>
+      <c r="E15">
+        <f>SUMIFS(tblMaster_Inputs[Helper_Amount], tblMaster_Inputs[Year], 2025, tblMaster_Inputs[Helper_Treatment], "SEC1250")</f>
+        <v/>
+      </c>
+      <c r="F15">
+        <f>SUMIFS(tblMaster_Inputs[Helper_Amount], tblMaster_Inputs[Year], 2026, tblMaster_Inputs[Helper_Treatment], "SEC1250")</f>
+        <v/>
+      </c>
+      <c r="G15">
+        <f>SUMIFS(tblMaster_Inputs[Helper_Amount], tblMaster_Inputs[Year], 2027, tblMaster_Inputs[Helper_Treatment], "SEC1250")</f>
+        <v/>
+      </c>
+      <c r="H15">
+        <f>SUMIFS(tblMaster_Inputs[Helper_Amount], tblMaster_Inputs[Year], 2028, tblMaster_Inputs[Helper_Treatment], "SEC1250")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:N63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1616,12 +3818,12 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>▸ STRATEGIES — tblY2025_Strategies</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>▸ 2025 ROLLUP — 1040 LINES</t>
         </is>
@@ -1746,7 +3948,7 @@
         <f>IF(ISBLANK(K6),J6,K6)+L6</f>
         <v/>
       </c>
-      <c r="N6" s="6">
+      <c r="N6" s="8">
         <f>HYPERLINK("#Y2025!I49", "↗ drill")</f>
         <v/>
       </c>
@@ -1802,7 +4004,7 @@
         <f>IF(ISBLANK(K7),J7,K7)</f>
         <v/>
       </c>
-      <c r="N7" s="6">
+      <c r="N7" s="8">
         <f>HYPERLINK("#Y2025!I49", "↗ drill")</f>
         <v/>
       </c>
@@ -1859,7 +4061,7 @@
         <f>IF(ISBLANK(K8),J8,K8)+L8</f>
         <v/>
       </c>
-      <c r="N8" s="6">
+      <c r="N8" s="8">
         <f>HYPERLINK("#Y2025!I49", "↗ drill")</f>
         <v/>
       </c>
@@ -1915,7 +4117,7 @@
         <f>IF(ISBLANK(K9),J9,K9)</f>
         <v/>
       </c>
-      <c r="N9" s="6">
+      <c r="N9" s="8">
         <f>HYPERLINK("#Y2025!I49", "↗ drill")</f>
         <v/>
       </c>
@@ -1972,7 +4174,7 @@
         <f>IF(ISBLANK(K10),J10,K10)+L10</f>
         <v/>
       </c>
-      <c r="N10" s="6">
+      <c r="N10" s="8">
         <f>HYPERLINK("#Y2025!I49", "↗ drill")</f>
         <v/>
       </c>
@@ -2001,7 +4203,7 @@
         <f>IF(ISBLANK(K11),J11,K11)+L11</f>
         <v/>
       </c>
-      <c r="N11" s="6">
+      <c r="N11" s="8">
         <f>HYPERLINK("#Y2025!I49", "↗ drill")</f>
         <v/>
       </c>
@@ -2030,7 +4232,7 @@
         <f>IF(ISBLANK(K12),J12,K12)+L12</f>
         <v/>
       </c>
-      <c r="N12" s="6">
+      <c r="N12" s="8">
         <f>HYPERLINK("#Y2025!I49", "↗ drill")</f>
         <v/>
       </c>
@@ -2058,7 +4260,7 @@
         <f>IF(ISBLANK(K13),J13,K13)</f>
         <v/>
       </c>
-      <c r="N13" s="6">
+      <c r="N13" s="8">
         <f>HYPERLINK("#Y2025!I49", "↗ drill")</f>
         <v/>
       </c>
@@ -2087,7 +4289,7 @@
         <f>IF(ISBLANK(K14),J14,K14)+L14</f>
         <v/>
       </c>
-      <c r="N14" s="6">
+      <c r="N14" s="8">
         <f>HYPERLINK("#Y2025!I49", "↗ drill")</f>
         <v/>
       </c>
@@ -2115,7 +4317,7 @@
         <f>IF(ISBLANK(K15),J15,K15)</f>
         <v/>
       </c>
-      <c r="N15" s="6">
+      <c r="N15" s="8">
         <f>HYPERLINK("#Y2025!I49", "↗ drill")</f>
         <v/>
       </c>
@@ -2144,7 +4346,7 @@
         <f>IF(ISBLANK(K16),J16,K16)+L16</f>
         <v/>
       </c>
-      <c r="N16" s="6">
+      <c r="N16" s="8">
         <f>HYPERLINK("#Y2025!I49", "↗ drill")</f>
         <v/>
       </c>
@@ -2173,7 +4375,7 @@
         <f>IF(ISBLANK(K17),J17,K17)+L17</f>
         <v/>
       </c>
-      <c r="N17" s="6">
+      <c r="N17" s="8">
         <f>HYPERLINK("#Y2025!I49", "↗ drill")</f>
         <v/>
       </c>
@@ -2201,13 +4403,13 @@
         <f>IF(ISBLANK(K18),J18,K18)</f>
         <v/>
       </c>
-      <c r="N18" s="6">
+      <c r="N18" s="8">
         <f>HYPERLINK("#Y2025!I49", "↗ drill")</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="H21" s="5" t="inlineStr">
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>▸ HELPER / TAX-CALC INPUTS — does NOT add to income; reference values for future LAMBDAs</t>
         </is>
@@ -2236,7 +4438,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="H23" s="7" t="inlineStr">
+      <c r="H23" s="9" t="inlineStr">
         <is>
           <t>W2_OWNER</t>
         </is>
@@ -2257,7 +4459,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="H24" s="7" t="inlineStr">
+      <c r="H24" s="9" t="inlineStr">
         <is>
           <t>W2_THIRD_PARTY</t>
         </is>
@@ -2278,7 +4480,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="H25" s="7" t="inlineStr">
+      <c r="H25" s="9" t="inlineStr">
         <is>
           <t>W2_TOTAL</t>
         </is>
@@ -2299,7 +4501,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="H26" s="7" t="inlineStr">
+      <c r="H26" s="9" t="inlineStr">
         <is>
           <t>BI_SE_SUBJECT</t>
         </is>
@@ -2320,7 +4522,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="H27" s="7" t="inlineStr">
+      <c r="H27" s="9" t="inlineStr">
         <is>
           <t>BI_ACTIVE_NONSE</t>
         </is>
@@ -2341,7 +4543,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="H28" s="7" t="inlineStr">
+      <c r="H28" s="9" t="inlineStr">
         <is>
           <t>BI_PASSIVE</t>
         </is>
@@ -2362,7 +4564,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="H29" s="7" t="inlineStr">
+      <c r="H29" s="9" t="inlineStr">
         <is>
           <t>TAX_EXEMPT</t>
         </is>
@@ -2383,7 +4585,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="H30" s="7" t="inlineStr">
+      <c r="H30" s="9" t="inlineStr">
         <is>
           <t>QUAL_DIV</t>
         </is>
@@ -2404,7 +4606,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="H31" s="7" t="inlineStr">
+      <c r="H31" s="9" t="inlineStr">
         <is>
           <t>CG_LT</t>
         </is>
@@ -2425,7 +4627,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="H32" s="7" t="inlineStr">
+      <c r="H32" s="9" t="inlineStr">
         <is>
           <t>CG_ST</t>
         </is>
@@ -2446,7 +4648,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="H33" s="7" t="inlineStr">
+      <c r="H33" s="9" t="inlineStr">
         <is>
           <t>SEC1250</t>
         </is>
@@ -2467,7 +4669,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="H35" s="5" t="inlineStr">
+      <c r="H35" s="7" t="inlineStr">
         <is>
           <t>▸ TAX CALC INPUTS — derived; each row is a workbook-level named range for LAMBDAs to consume</t>
         </is>
@@ -2496,7 +4698,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="H37" s="7" t="inlineStr">
+      <c r="H37" s="9" t="inlineStr">
         <is>
           <t>OrdIncome</t>
         </is>
@@ -2517,7 +4719,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="H38" s="7" t="inlineStr">
+      <c r="H38" s="9" t="inlineStr">
         <is>
           <t>MAGI</t>
         </is>
@@ -2538,7 +4740,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="H39" s="7" t="inlineStr">
+      <c r="H39" s="9" t="inlineStr">
         <is>
           <t>NII</t>
         </is>
@@ -2559,7 +4761,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="H40" s="7" t="inlineStr">
+      <c r="H40" s="9" t="inlineStr">
         <is>
           <t>QBI_Income</t>
         </is>
@@ -2580,7 +4782,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="H41" s="7" t="inlineStr">
+      <c r="H41" s="9" t="inlineStr">
         <is>
           <t>TaxableIncome_BeforeQBI</t>
         </is>
@@ -2601,7 +4803,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="H42" s="7" t="inlineStr">
+      <c r="H42" s="9" t="inlineStr">
         <is>
           <t>BusinessLoss</t>
         </is>
@@ -2622,7 +4824,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="H43" s="7" t="inlineStr">
+      <c r="H43" s="9" t="inlineStr">
         <is>
           <t>NetSEIncome</t>
         </is>
@@ -2643,7 +4845,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="H44" s="7" t="inlineStr">
+      <c r="H44" s="9" t="inlineStr">
         <is>
           <t>UBIA</t>
         </is>
@@ -2663,7 +4865,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="H45" s="7" t="inlineStr">
+      <c r="H45" s="9" t="inlineStr">
         <is>
           <t>IsSSTB</t>
         </is>
@@ -2683,7 +4885,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="H46" s="7" t="inlineStr">
+      <c r="H46" s="9" t="inlineStr">
         <is>
           <t>NOL_Carryforward</t>
         </is>
@@ -2703,24 +4905,24 @@
       </c>
     </row>
     <row r="48">
-      <c r="H48" s="5" t="inlineStr">
+      <c r="H48" s="7" t="inlineStr">
         <is>
           <t>▸ DRILL DETAIL — pick a line; FILTER below shows the contributing Master_Inputs rows</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="H49" s="8" t="inlineStr">
+      <c r="H49" s="10" t="inlineStr">
         <is>
           <t>Drill into line:</t>
         </is>
       </c>
-      <c r="I49" s="9" t="inlineStr">
+      <c r="I49" s="11" t="inlineStr">
         <is>
           <t>1z</t>
         </is>
       </c>
-      <c r="K49" s="6">
+      <c r="K49" s="8">
         <f>HYPERLINK("#Master_Inputs!A1", "✏ open Master_Inputs to edit")</f>
         <v/>
       </c>
@@ -2794,7 +4996,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4474,7 +6676,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4505,32 +6707,32 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Bucket</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>Yes_No</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>NIIT_Class</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>Provenance</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>TaxLines</t>
         </is>
@@ -4752,49 +6954,49 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>▸ PER-BUCKET TREATMENT_PROFILE LISTS</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>BusinessIncome_Profiles</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>Wages_Profiles</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>InvestmentIncome_Profiles</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>CapitalGains_Profiles</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr">
         <is>
           <t>Adjustment_Profiles</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr">
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>Itemized_Profiles</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="12" t="inlineStr">
         <is>
           <t>Credit_Profiles</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H18" s="12" t="inlineStr">
         <is>
           <t>Payment_Profiles</t>
         </is>
@@ -4989,49 +7191,49 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>▸ PER-BUCKET SOURCE_DOCUMENT LISTS</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t>BusinessIncome_Docs</t>
         </is>
       </c>
-      <c r="B34" s="10" t="inlineStr">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>Wages_Docs</t>
         </is>
       </c>
-      <c r="C34" s="10" t="inlineStr">
+      <c r="C34" s="12" t="inlineStr">
         <is>
           <t>InvestmentIncome_Docs</t>
         </is>
       </c>
-      <c r="D34" s="10" t="inlineStr">
+      <c r="D34" s="12" t="inlineStr">
         <is>
           <t>CapitalGains_Docs</t>
         </is>
       </c>
-      <c r="E34" s="10" t="inlineStr">
+      <c r="E34" s="12" t="inlineStr">
         <is>
           <t>Adjustment_Docs</t>
         </is>
       </c>
-      <c r="F34" s="10" t="inlineStr">
+      <c r="F34" s="12" t="inlineStr">
         <is>
           <t>Itemized_Docs</t>
         </is>
       </c>
-      <c r="G34" s="10" t="inlineStr">
+      <c r="G34" s="12" t="inlineStr">
         <is>
           <t>Credit_Docs</t>
         </is>
       </c>
-      <c r="H34" s="10" t="inlineStr">
+      <c r="H34" s="12" t="inlineStr">
         <is>
           <t>Payment_Docs</t>
         </is>

--- a/docs/Master_Pivot_Framework.xlsx
+++ b/docs/Master_Pivot_Framework.xlsx
@@ -23,6 +23,7 @@
     <definedName name="Provenance">'Dropdown_Lists'!$D$4:$D$13</definedName>
     <definedName name="Status">'Dropdown_Lists'!$E$4:$E$8</definedName>
     <definedName name="TaxLines">'Dropdown_Lists'!$F$4:$F$13</definedName>
+    <definedName name="Activity_Type">'Dropdown_Lists'!$G$4:$G$5</definedName>
     <definedName name="BusinessIncome_Profiles">'Dropdown_Lists'!$A$19:$A$27</definedName>
     <definedName name="Wages_Profiles">'Dropdown_Lists'!$B$19:$B$20</definedName>
     <definedName name="InvestmentIncome_Profiles">'Dropdown_Lists'!$C$19:$C$22</definedName>
@@ -262,9 +263,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblMaster_Inputs" displayName="tblMaster_Inputs" ref="A4:R14" headerRowCount="1">
-  <autoFilter ref="A4:R14"/>
-  <tableColumns count="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblMaster_Inputs" displayName="tblMaster_Inputs" ref="A4:S15" headerRowCount="1">
+  <autoFilter ref="A4:S15"/>
+  <tableColumns count="19">
     <tableColumn id="1" name="InputID"/>
     <tableColumn id="2" name="Year"/>
     <tableColumn id="3" name="ClientID"/>
@@ -272,17 +273,18 @@
     <tableColumn id="5" name="Bucket"/>
     <tableColumn id="6" name="Treatment_Profile"/>
     <tableColumn id="7" name="Source_Document"/>
-    <tableColumn id="8" name="Provenance"/>
-    <tableColumn id="9" name="Payor"/>
-    <tableColumn id="10" name="Baseline_Amount"/>
-    <tableColumn id="11" name="Helper_Amount"/>
-    <tableColumn id="12" name="SE_Subject"/>
-    <tableColumn id="13" name="NIIT_Class"/>
-    <tableColumn id="14" name="QBI_Eligible"/>
-    <tableColumn id="15" name="Primary_Line"/>
-    <tableColumn id="16" name="Helper_Treatment"/>
-    <tableColumn id="17" name="Consider"/>
-    <tableColumn id="18" name="Notes"/>
+    <tableColumn id="8" name="Activity_Type"/>
+    <tableColumn id="9" name="Provenance"/>
+    <tableColumn id="10" name="Payor"/>
+    <tableColumn id="11" name="Baseline_Amount"/>
+    <tableColumn id="12" name="Helper_Amount"/>
+    <tableColumn id="13" name="SE_Subject"/>
+    <tableColumn id="14" name="NIIT_Class"/>
+    <tableColumn id="15" name="QBI_Eligible"/>
+    <tableColumn id="16" name="Primary_Line"/>
+    <tableColumn id="17" name="Helper_Treatment"/>
+    <tableColumn id="18" name="Consider"/>
+    <tableColumn id="19" name="Notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -610,7 +612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -620,17 +622,18 @@
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="30" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
+    <col width="30" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -685,55 +688,60 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
+          <t>Activity_Type</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
           <t>Provenance</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Payor</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Baseline_Amount</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Helper_Amount</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>SE_Subject</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>NIIT_Class</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>QBI_Eligible</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="P4" s="3" t="inlineStr">
         <is>
           <t>Primary_Line</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="Q4" s="3" t="inlineStr">
         <is>
           <t>Helper_Treatment</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="R4" s="3" t="inlineStr">
         <is>
           <t>Consider</t>
         </is>
       </c>
-      <c r="R4" s="3" t="inlineStr">
+      <c r="S4" s="3" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -775,51 +783,56 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
           <t>PBC - Reviewed</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>Acme S-Corp</t>
         </is>
       </c>
-      <c r="J5" s="4" t="n">
+      <c r="K5" s="4" t="n">
         <v>153648</v>
       </c>
-      <c r="K5" s="4" t="n">
+      <c r="L5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
           <t>1z</t>
         </is>
       </c>
-      <c r="P5" s="4" t="inlineStr">
+      <c r="Q5" s="4" t="inlineStr">
         <is>
           <t>OWNER_PAY</t>
         </is>
       </c>
-      <c r="Q5" s="4" t="inlineStr">
+      <c r="R5" s="4" t="inlineStr">
         <is>
           <t>Owner reasonable comp</t>
         </is>
       </c>
-      <c r="R5" s="4" t="inlineStr"/>
+      <c r="S5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -857,51 +870,56 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
           <t>PBC - Reviewed</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>Cedillo Partnership</t>
         </is>
       </c>
-      <c r="J6" s="4" t="n">
+      <c r="K6" s="4" t="n">
         <v>-100766</v>
       </c>
-      <c r="K6" s="4" t="n">
+      <c r="L6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
           <t>Passive</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="O6" s="4" t="inlineStr">
+      <c r="P6" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="P6" s="4" t="inlineStr">
+      <c r="Q6" s="4" t="inlineStr">
         <is>
           <t>K1_SPLIT</t>
         </is>
       </c>
-      <c r="Q6" s="4" t="inlineStr">
+      <c r="R6" s="4" t="inlineStr">
         <is>
           <t>Passive loss</t>
         </is>
       </c>
-      <c r="R6" s="4" t="inlineStr"/>
+      <c r="S6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -939,51 +957,56 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
           <t>PBC - Reviewed</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>Brokerage</t>
         </is>
       </c>
-      <c r="J7" s="4" t="n">
+      <c r="K7" s="4" t="n">
         <v>25922</v>
       </c>
-      <c r="K7" s="4" t="n">
+      <c r="L7" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
           <t>Portfolio</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P7" s="4" t="inlineStr">
+        <is>
           <t>3b</t>
         </is>
       </c>
-      <c r="P7" s="4" t="inlineStr">
+      <c r="Q7" s="4" t="inlineStr">
         <is>
           <t>QUAL_DIV</t>
         </is>
       </c>
-      <c r="Q7" s="4" t="inlineStr">
+      <c r="R7" s="4" t="inlineStr">
         <is>
           <t>All non-qualified</t>
         </is>
       </c>
-      <c r="R7" s="4" t="inlineStr"/>
+      <c r="S7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -1021,51 +1044,56 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
           <t>PBC - Reviewed</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>Brokerage</t>
         </is>
       </c>
-      <c r="J8" s="4" t="n">
+      <c r="K8" s="4" t="n">
         <v>14487</v>
       </c>
-      <c r="K8" s="4" t="n">
+      <c r="L8" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
           <t>Portfolio</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P8" s="4" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="P8" s="4" t="inlineStr">
+      <c r="Q8" s="4" t="inlineStr">
         <is>
           <t>LTCG_SPLIT</t>
         </is>
       </c>
-      <c r="Q8" s="4" t="inlineStr">
+      <c r="R8" s="4" t="inlineStr">
         <is>
           <t>All long-term</t>
         </is>
       </c>
-      <c r="R8" s="4" t="inlineStr"/>
+      <c r="S8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1103,51 +1131,56 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
           <t>Estimate - Preparer</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>SampleCo S-Corp</t>
         </is>
-      </c>
-      <c r="J9" s="4" t="n">
-        <v>100000</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>100000</v>
       </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+      <c r="L9" s="4" t="n">
+        <v>100000</v>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="inlineStr">
+        <is>
           <t>1z</t>
         </is>
       </c>
-      <c r="P9" s="4" t="inlineStr">
+      <c r="Q9" s="4" t="inlineStr">
         <is>
           <t>OWNER_PAY</t>
         </is>
       </c>
-      <c r="Q9" s="4" t="inlineStr">
+      <c r="R9" s="4" t="inlineStr">
         <is>
           <t>Owner reasonable comp</t>
         </is>
       </c>
-      <c r="R9" s="4" t="inlineStr"/>
+      <c r="S9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -1185,51 +1218,56 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
           <t>PY Rolled Forward</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>SampleCo S-Corp K-1</t>
         </is>
       </c>
-      <c r="J10" s="4" t="n">
+      <c r="K10" s="4" t="n">
         <v>200000</v>
       </c>
-      <c r="K10" s="4" t="n">
+      <c r="L10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L10" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="O10" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="O10" s="4" t="inlineStr">
+      <c r="P10" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="P10" s="4" t="inlineStr">
+      <c r="Q10" s="4" t="inlineStr">
         <is>
           <t>K1_SPLIT</t>
         </is>
       </c>
-      <c r="Q10" s="4" t="inlineStr">
+      <c r="R10" s="4" t="inlineStr">
         <is>
           <t>Active S-corp K-1</t>
         </is>
       </c>
-      <c r="R10" s="4" t="inlineStr"/>
+      <c r="S10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1267,51 +1305,56 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
           <t>PBC - Received</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>Brokerage</t>
         </is>
       </c>
-      <c r="J11" s="4" t="n">
+      <c r="K11" s="4" t="n">
         <v>10000</v>
       </c>
-      <c r="K11" s="4" t="n">
+      <c r="L11" s="4" t="n">
         <v>7000</v>
       </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
           <t>Portfolio</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P11" s="4" t="inlineStr">
+        <is>
           <t>3b</t>
         </is>
       </c>
-      <c r="P11" s="4" t="inlineStr">
+      <c r="Q11" s="4" t="inlineStr">
         <is>
           <t>QUAL_DIV</t>
         </is>
       </c>
-      <c r="Q11" s="4" t="inlineStr">
+      <c r="R11" s="4" t="inlineStr">
         <is>
           <t>$7K qualified</t>
         </is>
       </c>
-      <c r="R11" s="4" t="inlineStr"/>
+      <c r="S11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -1349,51 +1392,56 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
           <t>PBC - Received</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>Brokerage</t>
         </is>
       </c>
-      <c r="J12" s="4" t="n">
+      <c r="K12" s="4" t="n">
         <v>500</v>
       </c>
-      <c r="K12" s="4" t="n">
+      <c r="L12" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
           <t>Portfolio</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P12" s="4" t="inlineStr">
+        <is>
           <t>2b</t>
         </is>
       </c>
-      <c r="P12" s="4" t="inlineStr">
+      <c r="Q12" s="4" t="inlineStr">
         <is>
           <t>TAX_EXEMPT</t>
         </is>
       </c>
-      <c r="Q12" s="4" t="inlineStr">
+      <c r="R12" s="4" t="inlineStr">
         <is>
           <t>All taxable</t>
         </is>
       </c>
-      <c r="R12" s="4" t="inlineStr"/>
+      <c r="S12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1431,51 +1479,56 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
           <t>PBC - Requested</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>Brokerage</t>
         </is>
       </c>
-      <c r="J13" s="4" t="n">
+      <c r="K13" s="4" t="n">
         <v>25000</v>
       </c>
-      <c r="K13" s="4" t="n">
+      <c r="L13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
           <t>Portfolio</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P13" s="4" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="P13" s="4" t="inlineStr">
+      <c r="Q13" s="4" t="inlineStr">
         <is>
           <t>LTCG_SPLIT</t>
         </is>
       </c>
-      <c r="Q13" s="4" t="inlineStr">
+      <c r="R13" s="4" t="inlineStr">
         <is>
           <t>All long-term</t>
         </is>
       </c>
-      <c r="R13" s="4" t="inlineStr"/>
+      <c r="S13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1513,50 +1566,138 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
           <t>PBC - Received</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr"/>
-      <c r="J14" s="4" t="n">
+      <c r="J14" s="4" t="inlineStr"/>
+      <c r="K14" s="4" t="n">
         <v>10000</v>
       </c>
-      <c r="K14" s="4" t="n">
+      <c r="L14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P14" s="4" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P14" s="4" t="inlineStr">
+      <c r="Q14" s="4" t="inlineStr">
         <is>
           <t>SALT</t>
         </is>
       </c>
-      <c r="Q14" s="4" t="inlineStr">
+      <c r="R14" s="4" t="inlineStr">
         <is>
           <t>SALT cap</t>
         </is>
       </c>
-      <c r="R14" s="4" t="inlineStr"/>
+      <c r="S14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SAM|2025|Strategy|CostSeg|01</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>SAMPLE</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Sample Client</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Business Income</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>SchE_Rental</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Strategy</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>Estimate - Preparer</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr"/>
+      <c r="K15" s="4" t="n">
+        <v>-80000</v>
+      </c>
+      <c r="L15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="O15" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P15" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Q15" s="4" t="inlineStr">
+        <is>
+          <t>PASSIVE</t>
+        </is>
+      </c>
+      <c r="R15" s="4" t="inlineStr">
+        <is>
+          <t>Cost Seg accelerated depreciation</t>
+        </is>
+      </c>
+      <c r="S15" s="4" t="inlineStr">
+        <is>
+          <t>STD-012 Committed</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="7">
+  <dataValidations count="8">
     <dataValidation sqref="E5:E500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Bucket</formula1>
     </dataValidation>
@@ -1567,15 +1708,18 @@
       <formula1>=INDIRECT(SUBSTITUTE($E5," ","")&amp;"_Docs")</formula1>
     </dataValidation>
     <dataValidation sqref="H5:H500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Activity_Type</formula1>
+    </dataValidation>
+    <dataValidation sqref="I5:I500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Provenance</formula1>
     </dataValidation>
-    <dataValidation sqref="L5:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Yes_No</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N5:N500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=NIIT_Class</formula1>
     </dataValidation>
-    <dataValidation sqref="N5:N500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O5:O500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Yes_No</formula1>
     </dataValidation>
   </dataValidations>
@@ -6737,6 +6881,11 @@
           <t>TaxLines</t>
         </is>
       </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>Activity_Type</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6769,6 +6918,11 @@
           <t>1z</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6799,6 +6953,11 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>2a</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Strategy</t>
         </is>
       </c>
     </row>

--- a/docs/Master_Pivot_Framework.xlsx
+++ b/docs/Master_Pivot_Framework.xlsx
@@ -83,7 +83,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -127,6 +127,11 @@
       <b val="1"/>
     </font>
     <font>
+      <b val="1"/>
+      <color rgb="000563C1"/>
+      <u val="single"/>
+    </font>
+    <font>
       <i val="1"/>
       <color rgb="00595959"/>
     </font>
@@ -166,7 +171,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -174,17 +179,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1736,7 +1742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1747,6 +1753,7 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1762,6 +1769,10 @@
           <t>Pure baseline aggregation. No overrides, no strategies. Year sheets handle those locally.</t>
         </is>
       </c>
+      <c r="I2" s="5">
+        <f>HYPERLINK("#Master_Inputs!A1", "↗ Edit in Master_Inputs")</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -1986,37 +1997,37 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>TOTAL INCOME</t>
         </is>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="6">
         <f>C5+C6+C7+C8+C9</f>
         <v/>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="6">
         <f>D5+D6+D7+D8+D9</f>
         <v/>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="6">
         <f>E5+E6+E7+E8+E9</f>
         <v/>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="6">
         <f>F5+F6+F7+F8+F9</f>
         <v/>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="6">
         <f>G5+G6+G7+G8+G9</f>
         <v/>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="6">
         <f>H5+H6+H7+H8+H9</f>
         <v/>
       </c>
@@ -2058,37 +2069,37 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>AGI</t>
         </is>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="6">
         <f>C10+C11</f>
         <v/>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="6">
         <f>D10+D11</f>
         <v/>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="6">
         <f>E10+E11</f>
         <v/>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="6">
         <f>F10+F11</f>
         <v/>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="6">
         <f>G10+G11</f>
         <v/>
       </c>
-      <c r="H12" s="5">
+      <c r="H12" s="6">
         <f>H10+H11</f>
         <v/>
       </c>
@@ -2166,42 +2177,123 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>TAXABLE INCOME</t>
         </is>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="6">
         <f>C12+C13+C14</f>
         <v/>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="6">
         <f>D12+D13+D14</f>
         <v/>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="6">
         <f>E12+E13+E14</f>
         <v/>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="6">
         <f>F12+F13+F14</f>
         <v/>
       </c>
-      <c r="G15" s="5">
+      <c r="G15" s="6">
         <f>G12+G13+G14</f>
         <v/>
       </c>
-      <c r="H15" s="5">
+      <c r="H15" s="6">
         <f>H12+H13+H14</f>
         <v/>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>▸ DRILL DETAIL — pick a line, FILTER below shows contributing Master_Inputs rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>Drill into row:</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>1z</t>
+        </is>
+      </c>
+      <c r="I19" s="10">
+        <f>HYPERLINK("#Master_Inputs!A1", "✏ open Master_Inputs")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>InputID</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Bucket</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Treatment_Profile</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Payor</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Baseline_Amount</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Helper_Amount</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Activity_Type</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <f>IFERROR(HSTACK(FILTER(tblMaster_Inputs[InputID],            tblMaster_Inputs[Primary_Line]=$B$19),FILTER(tblMaster_Inputs[Year],               tblMaster_Inputs[Primary_Line]=$B$19),FILTER(tblMaster_Inputs[Bucket],             tblMaster_Inputs[Primary_Line]=$B$19),FILTER(tblMaster_Inputs[Treatment_Profile],  tblMaster_Inputs[Primary_Line]=$B$19),FILTER(tblMaster_Inputs[Payor],              tblMaster_Inputs[Primary_Line]=$B$19),FILTER(tblMaster_Inputs[Baseline_Amount],    tblMaster_Inputs[Primary_Line]=$B$19),FILTER(tblMaster_Inputs[Helper_Amount],      tblMaster_Inputs[Primary_Line]=$B$19),FILTER(tblMaster_Inputs[Activity_Type],      tblMaster_Inputs[Primary_Line]=$B$19),FILTER(tblMaster_Inputs[Notes],              tblMaster_Inputs[Primary_Line]=$B$19)), "(no matching rows for this drill value)")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"1z,2,3,7,8,10,12,13"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2212,7 +2304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2223,6 +2315,7 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2238,6 +2331,10 @@
           <t>Same as summary but Line 8 broken into Schedule C / Schedule E rental / Partnership K-1 / S-Corp K-1 / Sch F / Trust K-1.</t>
         </is>
       </c>
+      <c r="I2" s="5">
+        <f>HYPERLINK("#Master_Inputs!A1", "↗ Edit in Master_Inputs")</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -2642,73 +2739,73 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Other income (Line 8 total)</t>
         </is>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="6">
         <f>C9+C10+C11+C12+C13+C14</f>
         <v/>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="6">
         <f>D9+D10+D11+D12+D13+D14</f>
         <v/>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="6">
         <f>E9+E10+E11+E12+E13+E14</f>
         <v/>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="6">
         <f>F9+F10+F11+F12+F13+F14</f>
         <v/>
       </c>
-      <c r="G15" s="5">
+      <c r="G15" s="6">
         <f>G9+G10+G11+G12+G13+G14</f>
         <v/>
       </c>
-      <c r="H15" s="5">
+      <c r="H15" s="6">
         <f>H9+H10+H11+H12+H13+H14</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>TOTAL INCOME</t>
         </is>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="6">
         <f>C5+C6+C7+C8+C15</f>
         <v/>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="6">
         <f>D5+D6+D7+D8+D15</f>
         <v/>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="6">
         <f>E5+E6+E7+E8+E15</f>
         <v/>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="6">
         <f>F5+F6+F7+F8+F15</f>
         <v/>
       </c>
-      <c r="G16" s="5">
+      <c r="G16" s="6">
         <f>G5+G6+G7+G8+G15</f>
         <v/>
       </c>
-      <c r="H16" s="5">
+      <c r="H16" s="6">
         <f>H5+H6+H7+H8+H15</f>
         <v/>
       </c>
@@ -2750,37 +2847,37 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>AGI</t>
         </is>
       </c>
-      <c r="C18" s="5">
+      <c r="C18" s="6">
         <f>C16+C17</f>
         <v/>
       </c>
-      <c r="D18" s="5">
+      <c r="D18" s="6">
         <f>D16+D17</f>
         <v/>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="6">
         <f>E16+E17</f>
         <v/>
       </c>
-      <c r="F18" s="5">
+      <c r="F18" s="6">
         <f>F16+F17</f>
         <v/>
       </c>
-      <c r="G18" s="5">
+      <c r="G18" s="6">
         <f>G16+G17</f>
         <v/>
       </c>
-      <c r="H18" s="5">
+      <c r="H18" s="6">
         <f>H16+H17</f>
         <v/>
       </c>
@@ -2858,42 +2955,123 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>TAXABLE INCOME</t>
         </is>
       </c>
-      <c r="C21" s="5">
+      <c r="C21" s="6">
         <f>C18+C19+C20</f>
         <v/>
       </c>
-      <c r="D21" s="5">
+      <c r="D21" s="6">
         <f>D18+D19+D20</f>
         <v/>
       </c>
-      <c r="E21" s="5">
+      <c r="E21" s="6">
         <f>E18+E19+E20</f>
         <v/>
       </c>
-      <c r="F21" s="5">
+      <c r="F21" s="6">
         <f>F18+F19+F20</f>
         <v/>
       </c>
-      <c r="G21" s="5">
+      <c r="G21" s="6">
         <f>G18+G19+G20</f>
         <v/>
       </c>
-      <c r="H21" s="5">
+      <c r="H21" s="6">
         <f>H18+H19+H20</f>
         <v/>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>▸ DRILL DETAIL — pick a line, FILTER below shows contributing Master_Inputs rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Drill into row:</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>1z</t>
+        </is>
+      </c>
+      <c r="I25" s="10">
+        <f>HYPERLINK("#Master_Inputs!A1", "✏ open Master_Inputs")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>InputID</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Bucket</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Treatment_Profile</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Payor</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Baseline_Amount</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Helper_Amount</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Activity_Type</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <f>IFERROR(HSTACK(FILTER(tblMaster_Inputs[InputID],            tblMaster_Inputs[Primary_Line]=$B$25),FILTER(tblMaster_Inputs[Year],               tblMaster_Inputs[Primary_Line]=$B$25),FILTER(tblMaster_Inputs[Bucket],             tblMaster_Inputs[Primary_Line]=$B$25),FILTER(tblMaster_Inputs[Treatment_Profile],  tblMaster_Inputs[Primary_Line]=$B$25),FILTER(tblMaster_Inputs[Payor],              tblMaster_Inputs[Primary_Line]=$B$25),FILTER(tblMaster_Inputs[Baseline_Amount],    tblMaster_Inputs[Primary_Line]=$B$25),FILTER(tblMaster_Inputs[Helper_Amount],      tblMaster_Inputs[Primary_Line]=$B$25),FILTER(tblMaster_Inputs[Activity_Type],      tblMaster_Inputs[Primary_Line]=$B$25),FILTER(tblMaster_Inputs[Notes],              tblMaster_Inputs[Primary_Line]=$B$25)), "(no matching rows for this drill value)")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"1z,2,3,7,8.SchC,8.SchE,8.PTP,8.SCorp,8.SchF,8.Trust,10,12,13"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2904,7 +3082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2915,6 +3093,7 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2930,6 +3109,10 @@
           <t>2a and 3a are informational (carve-outs of helpers); they don't add to Line 9 Total Income.</t>
         </is>
       </c>
+      <c r="I2" s="5">
+        <f>HYPERLINK("#Master_Inputs!A1", "↗ Edit in Master_Inputs")</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -3015,7 +3198,7 @@
           <t>2a</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Tax-exempt interest (informational)</t>
         </is>
@@ -3087,7 +3270,7 @@
           <t>3a</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>Qualified dividends (informational)</t>
         </is>
@@ -3226,37 +3409,37 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>TOTAL INCOME</t>
         </is>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="6">
         <f>C5+C7+C9+C10+C11</f>
         <v/>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="6">
         <f>D5+D7+D9+D10+D11</f>
         <v/>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="6">
         <f>E5+E7+E9+E10+E11</f>
         <v/>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="6">
         <f>F5+F7+F9+F10+F11</f>
         <v/>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="6">
         <f>G5+G7+G9+G10+G11</f>
         <v/>
       </c>
-      <c r="H12" s="5">
+      <c r="H12" s="6">
         <f>H5+H7+H9+H10+H11</f>
         <v/>
       </c>
@@ -3298,37 +3481,37 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>AGI</t>
         </is>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="6">
         <f>C12+C13</f>
         <v/>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="6">
         <f>D12+D13</f>
         <v/>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="6">
         <f>E12+E13</f>
         <v/>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="6">
         <f>F12+F13</f>
         <v/>
       </c>
-      <c r="G14" s="5">
+      <c r="G14" s="6">
         <f>G12+G13</f>
         <v/>
       </c>
-      <c r="H14" s="5">
+      <c r="H14" s="6">
         <f>H12+H13</f>
         <v/>
       </c>
@@ -3406,42 +3589,123 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>TAXABLE INCOME</t>
         </is>
       </c>
-      <c r="C17" s="5">
+      <c r="C17" s="6">
         <f>C14+C15+C16</f>
         <v/>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="6">
         <f>D14+D15+D16</f>
         <v/>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="6">
         <f>E14+E15+E16</f>
         <v/>
       </c>
-      <c r="F17" s="5">
+      <c r="F17" s="6">
         <f>F14+F15+F16</f>
         <v/>
       </c>
-      <c r="G17" s="5">
+      <c r="G17" s="6">
         <f>G14+G15+G16</f>
         <v/>
       </c>
-      <c r="H17" s="5">
+      <c r="H17" s="6">
         <f>H14+H15+H16</f>
         <v/>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>▸ DRILL DETAIL — pick a line, FILTER below shows contributing Master_Inputs rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Drill into row:</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>1z</t>
+        </is>
+      </c>
+      <c r="I21" s="10">
+        <f>HYPERLINK("#Master_Inputs!A1", "✏ open Master_Inputs")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>InputID</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Bucket</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Treatment_Profile</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Payor</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Baseline_Amount</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Helper_Amount</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Activity_Type</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <f>IFERROR(HSTACK(FILTER(tblMaster_Inputs[InputID],            tblMaster_Inputs[Primary_Line]=$B$21),FILTER(tblMaster_Inputs[Year],               tblMaster_Inputs[Primary_Line]=$B$21),FILTER(tblMaster_Inputs[Bucket],             tblMaster_Inputs[Primary_Line]=$B$21),FILTER(tblMaster_Inputs[Treatment_Profile],  tblMaster_Inputs[Primary_Line]=$B$21),FILTER(tblMaster_Inputs[Payor],              tblMaster_Inputs[Primary_Line]=$B$21),FILTER(tblMaster_Inputs[Baseline_Amount],    tblMaster_Inputs[Primary_Line]=$B$21),FILTER(tblMaster_Inputs[Helper_Amount],      tblMaster_Inputs[Primary_Line]=$B$21),FILTER(tblMaster_Inputs[Activity_Type],      tblMaster_Inputs[Primary_Line]=$B$21),FILTER(tblMaster_Inputs[Notes],              tblMaster_Inputs[Primary_Line]=$B$21)), "(no matching rows for this drill value)")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"1z,2a,2b,3a,3b,7,8,10,12,13"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3452,7 +3716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3463,6 +3727,7 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3478,6 +3743,10 @@
           <t>These exist for LAMBDA inputs only — qualified div for LTCG stacking, owner W-2 for FICA, etc.</t>
         </is>
       </c>
+      <c r="I2" s="5">
+        <f>HYPERLINK("#Master_Inputs!A1", "↗ Edit in Master_Inputs")</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -3594,37 +3863,37 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>W2_TOTAL</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Total W-2 (owner + third-party)</t>
         </is>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="6">
         <f>C5+C6</f>
         <v/>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="6">
         <f>D5+D6</f>
         <v/>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="6">
         <f>E5+E6</f>
         <v/>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="6">
         <f>F5+F6</f>
         <v/>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="6">
         <f>G5+G6</f>
         <v/>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="6">
         <f>H5+H6</f>
         <v/>
       </c>
@@ -3917,7 +4186,88 @@
         <v/>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>▸ DRILL DETAIL — pick a line, FILTER below shows contributing Master_Inputs rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>Drill into row:</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>W2_OWNER</t>
+        </is>
+      </c>
+      <c r="I19" s="10">
+        <f>HYPERLINK("#Master_Inputs!A1", "✏ open Master_Inputs")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>InputID</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Bucket</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Treatment_Profile</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Payor</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Baseline_Amount</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Helper_Amount</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Activity_Type</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <f>IFERROR(HSTACK(FILTER(tblMaster_Inputs[InputID],            tblMaster_Inputs[Helper_Treatment]=$B$19),FILTER(tblMaster_Inputs[Year],               tblMaster_Inputs[Helper_Treatment]=$B$19),FILTER(tblMaster_Inputs[Bucket],             tblMaster_Inputs[Helper_Treatment]=$B$19),FILTER(tblMaster_Inputs[Treatment_Profile],  tblMaster_Inputs[Helper_Treatment]=$B$19),FILTER(tblMaster_Inputs[Payor],              tblMaster_Inputs[Helper_Treatment]=$B$19),FILTER(tblMaster_Inputs[Baseline_Amount],    tblMaster_Inputs[Helper_Treatment]=$B$19),FILTER(tblMaster_Inputs[Helper_Amount],      tblMaster_Inputs[Helper_Treatment]=$B$19),FILTER(tblMaster_Inputs[Activity_Type],      tblMaster_Inputs[Helper_Treatment]=$B$19),FILTER(tblMaster_Inputs[Notes],              tblMaster_Inputs[Helper_Treatment]=$B$19)), "(no matching rows for this drill value)")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"W2_OWNER,W2_THIRD_PARTY,BI_SE_SUBJECT,BI_ACTIVE_NONSE,BI_PASSIVE,TAX_EXEMPT,QUAL_DIV,CG_LT,CG_ST,SEC1250"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4092,7 +4442,7 @@
         <f>IF(ISBLANK(K6),J6,K6)+L6</f>
         <v/>
       </c>
-      <c r="N6" s="8">
+      <c r="N6" s="10">
         <f>HYPERLINK("#Y2025!I49", "↗ drill")</f>
         <v/>
       </c>
@@ -4148,7 +4498,7 @@
         <f>IF(ISBLANK(K7),J7,K7)</f>
         <v/>
       </c>
-      <c r="N7" s="8">
+      <c r="N7" s="10">
         <f>HYPERLINK("#Y2025!I49", "↗ drill")</f>
         <v/>
       </c>
@@ -4205,7 +4555,7 @@
         <f>IF(ISBLANK(K8),J8,K8)+L8</f>
         <v/>
       </c>
-      <c r="N8" s="8">
+      <c r="N8" s="10">
         <f>HYPERLINK("#Y2025!I49", "↗ drill")</f>
         <v/>
       </c>
@@ -4261,7 +4611,7 @@
         <f>IF(ISBLANK(K9),J9,K9)</f>
         <v/>
       </c>
-      <c r="N9" s="8">
+      <c r="N9" s="10">
         <f>HYPERLINK("#Y2025!I49", "↗ drill")</f>
         <v/>
       </c>
@@ -4318,7 +4668,7 @@
         <f>IF(ISBLANK(K10),J10,K10)+L10</f>
         <v/>
       </c>
-      <c r="N10" s="8">
+      <c r="N10" s="10">
         <f>HYPERLINK("#Y2025!I49", "↗ drill")</f>
         <v/>
       </c>
@@ -4347,7 +4697,7 @@
         <f>IF(ISBLANK(K11),J11,K11)+L11</f>
         <v/>
       </c>
-      <c r="N11" s="8">
+      <c r="N11" s="10">
         <f>HYPERLINK("#Y2025!I49", "↗ drill")</f>
         <v/>
       </c>
@@ -4376,7 +4726,7 @@
         <f>IF(ISBLANK(K12),J12,K12)+L12</f>
         <v/>
       </c>
-      <c r="N12" s="8">
+      <c r="N12" s="10">
         <f>HYPERLINK("#Y2025!I49", "↗ drill")</f>
         <v/>
       </c>
@@ -4404,7 +4754,7 @@
         <f>IF(ISBLANK(K13),J13,K13)</f>
         <v/>
       </c>
-      <c r="N13" s="8">
+      <c r="N13" s="10">
         <f>HYPERLINK("#Y2025!I49", "↗ drill")</f>
         <v/>
       </c>
@@ -4433,7 +4783,7 @@
         <f>IF(ISBLANK(K14),J14,K14)+L14</f>
         <v/>
       </c>
-      <c r="N14" s="8">
+      <c r="N14" s="10">
         <f>HYPERLINK("#Y2025!I49", "↗ drill")</f>
         <v/>
       </c>
@@ -4461,7 +4811,7 @@
         <f>IF(ISBLANK(K15),J15,K15)</f>
         <v/>
       </c>
-      <c r="N15" s="8">
+      <c r="N15" s="10">
         <f>HYPERLINK("#Y2025!I49", "↗ drill")</f>
         <v/>
       </c>
@@ -4490,7 +4840,7 @@
         <f>IF(ISBLANK(K16),J16,K16)+L16</f>
         <v/>
       </c>
-      <c r="N16" s="8">
+      <c r="N16" s="10">
         <f>HYPERLINK("#Y2025!I49", "↗ drill")</f>
         <v/>
       </c>
@@ -4519,7 +4869,7 @@
         <f>IF(ISBLANK(K17),J17,K17)+L17</f>
         <v/>
       </c>
-      <c r="N17" s="8">
+      <c r="N17" s="10">
         <f>HYPERLINK("#Y2025!I49", "↗ drill")</f>
         <v/>
       </c>
@@ -4547,7 +4897,7 @@
         <f>IF(ISBLANK(K18),J18,K18)</f>
         <v/>
       </c>
-      <c r="N18" s="8">
+      <c r="N18" s="10">
         <f>HYPERLINK("#Y2025!I49", "↗ drill")</f>
         <v/>
       </c>
@@ -4582,7 +4932,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="H23" s="9" t="inlineStr">
+      <c r="H23" s="12" t="inlineStr">
         <is>
           <t>W2_OWNER</t>
         </is>
@@ -4603,7 +4953,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="H24" s="9" t="inlineStr">
+      <c r="H24" s="12" t="inlineStr">
         <is>
           <t>W2_THIRD_PARTY</t>
         </is>
@@ -4624,7 +4974,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="H25" s="9" t="inlineStr">
+      <c r="H25" s="12" t="inlineStr">
         <is>
           <t>W2_TOTAL</t>
         </is>
@@ -4645,7 +4995,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="H26" s="9" t="inlineStr">
+      <c r="H26" s="12" t="inlineStr">
         <is>
           <t>BI_SE_SUBJECT</t>
         </is>
@@ -4666,7 +5016,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="H27" s="9" t="inlineStr">
+      <c r="H27" s="12" t="inlineStr">
         <is>
           <t>BI_ACTIVE_NONSE</t>
         </is>
@@ -4687,7 +5037,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="H28" s="9" t="inlineStr">
+      <c r="H28" s="12" t="inlineStr">
         <is>
           <t>BI_PASSIVE</t>
         </is>
@@ -4708,7 +5058,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="H29" s="9" t="inlineStr">
+      <c r="H29" s="12" t="inlineStr">
         <is>
           <t>TAX_EXEMPT</t>
         </is>
@@ -4729,7 +5079,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="H30" s="9" t="inlineStr">
+      <c r="H30" s="12" t="inlineStr">
         <is>
           <t>QUAL_DIV</t>
         </is>
@@ -4750,7 +5100,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="H31" s="9" t="inlineStr">
+      <c r="H31" s="12" t="inlineStr">
         <is>
           <t>CG_LT</t>
         </is>
@@ -4771,7 +5121,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="H32" s="9" t="inlineStr">
+      <c r="H32" s="12" t="inlineStr">
         <is>
           <t>CG_ST</t>
         </is>
@@ -4792,7 +5142,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="H33" s="9" t="inlineStr">
+      <c r="H33" s="12" t="inlineStr">
         <is>
           <t>SEC1250</t>
         </is>
@@ -4842,7 +5192,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="H37" s="9" t="inlineStr">
+      <c r="H37" s="12" t="inlineStr">
         <is>
           <t>OrdIncome</t>
         </is>
@@ -4863,7 +5213,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="H38" s="9" t="inlineStr">
+      <c r="H38" s="12" t="inlineStr">
         <is>
           <t>MAGI</t>
         </is>
@@ -4884,7 +5234,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="H39" s="9" t="inlineStr">
+      <c r="H39" s="12" t="inlineStr">
         <is>
           <t>NII</t>
         </is>
@@ -4905,7 +5255,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="H40" s="9" t="inlineStr">
+      <c r="H40" s="12" t="inlineStr">
         <is>
           <t>QBI_Income</t>
         </is>
@@ -4926,7 +5276,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="H41" s="9" t="inlineStr">
+      <c r="H41" s="12" t="inlineStr">
         <is>
           <t>TaxableIncome_BeforeQBI</t>
         </is>
@@ -4947,7 +5297,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="H42" s="9" t="inlineStr">
+      <c r="H42" s="12" t="inlineStr">
         <is>
           <t>BusinessLoss</t>
         </is>
@@ -4968,7 +5318,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="H43" s="9" t="inlineStr">
+      <c r="H43" s="12" t="inlineStr">
         <is>
           <t>NetSEIncome</t>
         </is>
@@ -4989,7 +5339,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="H44" s="9" t="inlineStr">
+      <c r="H44" s="12" t="inlineStr">
         <is>
           <t>UBIA</t>
         </is>
@@ -5009,7 +5359,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="H45" s="9" t="inlineStr">
+      <c r="H45" s="12" t="inlineStr">
         <is>
           <t>IsSSTB</t>
         </is>
@@ -5029,7 +5379,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="H46" s="9" t="inlineStr">
+      <c r="H46" s="12" t="inlineStr">
         <is>
           <t>NOL_Carryforward</t>
         </is>
@@ -5056,17 +5406,17 @@
       </c>
     </row>
     <row r="49">
-      <c r="H49" s="10" t="inlineStr">
+      <c r="H49" s="8" t="inlineStr">
         <is>
           <t>Drill into line:</t>
         </is>
       </c>
-      <c r="I49" s="11" t="inlineStr">
+      <c r="I49" s="9" t="inlineStr">
         <is>
           <t>1z</t>
         </is>
       </c>
-      <c r="K49" s="8">
+      <c r="K49" s="10">
         <f>HYPERLINK("#Master_Inputs!A1", "✏ open Master_Inputs to edit")</f>
         <v/>
       </c>
@@ -6851,37 +7201,37 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Bucket</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Yes_No</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>NIIT_Class</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>Provenance</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>TaxLines</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>Activity_Type</t>
         </is>
@@ -7120,42 +7470,42 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>BusinessIncome_Profiles</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B18" s="13" t="inlineStr">
         <is>
           <t>Wages_Profiles</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t>InvestmentIncome_Profiles</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>CapitalGains_Profiles</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
         <is>
           <t>Adjustment_Profiles</t>
         </is>
       </c>
-      <c r="F18" s="12" t="inlineStr">
+      <c r="F18" s="13" t="inlineStr">
         <is>
           <t>Itemized_Profiles</t>
         </is>
       </c>
-      <c r="G18" s="12" t="inlineStr">
+      <c r="G18" s="13" t="inlineStr">
         <is>
           <t>Credit_Profiles</t>
         </is>
       </c>
-      <c r="H18" s="12" t="inlineStr">
+      <c r="H18" s="13" t="inlineStr">
         <is>
           <t>Payment_Profiles</t>
         </is>
@@ -7357,42 +7707,42 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="12" t="inlineStr">
+      <c r="A34" s="13" t="inlineStr">
         <is>
           <t>BusinessIncome_Docs</t>
         </is>
       </c>
-      <c r="B34" s="12" t="inlineStr">
+      <c r="B34" s="13" t="inlineStr">
         <is>
           <t>Wages_Docs</t>
         </is>
       </c>
-      <c r="C34" s="12" t="inlineStr">
+      <c r="C34" s="13" t="inlineStr">
         <is>
           <t>InvestmentIncome_Docs</t>
         </is>
       </c>
-      <c r="D34" s="12" t="inlineStr">
+      <c r="D34" s="13" t="inlineStr">
         <is>
           <t>CapitalGains_Docs</t>
         </is>
       </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="E34" s="13" t="inlineStr">
         <is>
           <t>Adjustment_Docs</t>
         </is>
       </c>
-      <c r="F34" s="12" t="inlineStr">
+      <c r="F34" s="13" t="inlineStr">
         <is>
           <t>Itemized_Docs</t>
         </is>
       </c>
-      <c r="G34" s="12" t="inlineStr">
+      <c r="G34" s="13" t="inlineStr">
         <is>
           <t>Credit_Docs</t>
         </is>
       </c>
-      <c r="H34" s="12" t="inlineStr">
+      <c r="H34" s="13" t="inlineStr">
         <is>
           <t>Payment_Docs</t>
         </is>

--- a/docs/Master_Pivot_Framework.xlsx
+++ b/docs/Master_Pivot_Framework.xlsx
@@ -8,13 +8,14 @@
   </bookViews>
   <sheets>
     <sheet name="Master_Inputs" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Pivot_Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Pivot_Medium" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Pivot_Detailed" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Pivot_Helpers" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Y2025" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Treatment_Profile_Map" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Dropdown_Lists" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Column_Definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Pivot_Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Pivot_Medium" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Pivot_Detailed" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Pivot_Helpers" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Y2025" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Treatment_Profile_Map" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Dropdown_Lists" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="Bucket">'Dropdown_Lists'!$A$4:$A$11</definedName>
@@ -22,8 +23,11 @@
     <definedName name="NIIT_Class">'Dropdown_Lists'!$C$4:$C$7</definedName>
     <definedName name="Provenance">'Dropdown_Lists'!$D$4:$D$13</definedName>
     <definedName name="Status">'Dropdown_Lists'!$E$4:$E$8</definedName>
-    <definedName name="TaxLines">'Dropdown_Lists'!$F$4:$F$13</definedName>
+    <definedName name="TaxLines">'Dropdown_Lists'!$F$4:$F$16</definedName>
     <definedName name="Activity_Type">'Dropdown_Lists'!$G$4:$G$5</definedName>
+    <definedName name="TaxYears">'Dropdown_Lists'!$H$4:$H$9</definedName>
+    <definedName name="Helper_Treatments">'Dropdown_Lists'!$I$4:$I$26</definedName>
+    <definedName name="Review_Status">'Dropdown_Lists'!$J$4:$J$7</definedName>
     <definedName name="BusinessIncome_Profiles">'Dropdown_Lists'!$A$19:$A$27</definedName>
     <definedName name="Wages_Profiles">'Dropdown_Lists'!$B$19:$B$20</definedName>
     <definedName name="InvestmentIncome_Profiles">'Dropdown_Lists'!$C$19:$C$22</definedName>
@@ -297,7 +301,24 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="tblY2025_Strategies" displayName="tblY2025_Strategies" ref="A5:F10" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="tblColumn_Definitions" displayName="tblColumn_Definitions" ref="A4:H23" headerRowCount="1">
+  <autoFilter ref="A4:H23"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="Col"/>
+    <tableColumn id="2" name="Column Name"/>
+    <tableColumn id="3" name="Data Type"/>
+    <tableColumn id="4" name="Required?"/>
+    <tableColumn id="5" name="Allowed Values / Source"/>
+    <tableColumn id="6" name="Auto-Fill?"/>
+    <tableColumn id="7" name="Definition"/>
+    <tableColumn id="8" name="Example"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="tblY2025_Strategies" displayName="tblY2025_Strategies" ref="A5:F10" headerRowCount="1">
   <autoFilter ref="A5:F10"/>
   <tableColumns count="6">
     <tableColumn id="1" name="StrategyID"/>
@@ -311,8 +332,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="tblTreatmentProfileMap" displayName="tblTreatmentProfileMap" ref="A4:I38" headerRowCount="1">
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="tblTreatmentProfileMap" displayName="tblTreatmentProfileMap" ref="A4:I38" headerRowCount="1">
   <autoFilter ref="A4:I38"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Profile"/>
@@ -1703,7 +1724,10 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="8">
+  <dataValidations count="11">
+    <dataValidation sqref="B5:B500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=TaxYears</formula1>
+    </dataValidation>
     <dataValidation sqref="E5:E500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Bucket</formula1>
     </dataValidation>
@@ -1728,6 +1752,12 @@
     <dataValidation sqref="O5:O500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Yes_No</formula1>
     </dataValidation>
+    <dataValidation sqref="P5:P500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=TaxLines</formula1>
+    </dataValidation>
+    <dataValidation sqref="Q5:Q500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Helper_Treatments</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -1737,6 +1767,887 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="65" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>COLUMN DEFINITIONS — Master_Inputs data dictionary</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Authoritative reference for every column on Master_Inputs. If a column is added/changed, update here first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Col</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Column Name</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Required?</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Allowed Values / Source</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Auto-Fill?</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Example</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>InputID</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Composite key — typically &lt;ClientID&gt;|&lt;Year&gt;|&lt;Bucket-short&gt;|&lt;seq&gt;</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Unique identifier for the row. Must be unique across the table.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>CED|2024|Wages|01</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Dropdown: =TaxYears (2023-2028)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tax year this row belongs to.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ClientID</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Short uppercase code (CED, SAM, etc.); should also exist on Clients sheet (when added)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Client identifier. Multiple rows per client per year.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>CEDILLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ClientName</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Free text</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Full client name. Could be auto-filled via VLOOKUP from Clients sheet once it exists.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Ron Cedillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Bucket</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Text (closed)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Dropdown: =Bucket (Business Income | Wages | Investment Income | Capital Gains | Adjustment | Itemized | Credit | Payment)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Top-level income/deduction category. Drives the cascading dropdowns for Treatment_Profile and Source_Document.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Business Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Treatment_Profile</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Text (closed)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>CASCADED dropdown: =INDIRECT(SUBSTITUTE($E,"","")&amp;"_Profiles") — narrows by Bucket</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Specific tax-treatment classification within the bucket (e.g., K1_PTP_Passive, W2_SCorpOwner). Drives SE_Subject, NIIT_Class, QBI_Eligible, Primary_Line, Helper_Treatment via Treatment_Profile_Map.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>K1_PTP_Passive</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Source_Document</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Text (closed)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>CASCADED dropdown: =INDIRECT(SUBSTITUTE($E," ","")&amp;"_Docs") — narrows by Bucket</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Underlying source document (W-2, K-1, 1099-DIV, etc.).</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>K-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Activity_Type</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Text (closed)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Dropdown: =Activity_Type (Baseline | Strategy)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Whether this row represents a baseline source-input fact, or an intentional tax strategy. Strategy rows are created by the strategy-commit macro.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Provenance</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Text (closed)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Dropdown: =Provenance (PY Rolled Forward, PY Actuals, Estimate-Preparer/Client, PBC-Requested/Received/Reviewed, Extraction-Imported/Tied, System Calculated)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Where this number came from / how confident we are. Drives PBC tracking.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>PBC - Reviewed</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Payor</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Text (free)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Free text — entity / employer / broker name</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Open-ended payor identifier.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Cedillo Partnership</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Baseline_Amount</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Number; positive for income, negative for losses/deductions</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Headline dollar amount. The primary aggregation field — pivots SUMIF over this column.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>153648</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Helper_Amount</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Number; the carve-out portion of Baseline_Amount that gets different tax treatment</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sub-portion of Baseline_Amount needing different treatment (qualified div of total div; tax-exempt int of total int; owner W-2 of total W-2; §1250 of LT gain).</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>7000</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SE_Subject</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Yes/No</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Yes (auto)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Dropdown: =Yes_No</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>YES — VBA auto-fills from Treatment_Profile via Treatment_Profile_Map[SE_Subject]</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Whether income on this row is subject to Self-Employment tax.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NIIT_Class</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Text (closed)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Yes (auto)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Dropdown: =NIIT_Class (Active | Passive | Portfolio | N/A)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>YES — VBA auto-fills from Treatment_Profile_Map[NIIT_Class]</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Classification for NIIT and passive-loss-allowance rules.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>QBI_Eligible</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Yes/No</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Yes (auto)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Dropdown: =Yes_No</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>YES — VBA auto-fills from Treatment_Profile_Map[QBI_Eligible]</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Whether this income qualifies for §199A QBI deduction.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Primary_Line</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Text (closed)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Yes (auto)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Dropdown: =TaxLines (1z, 2a, 2b, 3a, 3b, 7, 8, 9, 10, 11, 12, 13, 15)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>YES — VBA auto-fills from Treatment_Profile_Map[Primary_Line]</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Which 1040 line this row aggregates into.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Helper_Treatment</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Text (closed)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Yes (auto)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Dropdown: =Helper_Treatments (NONE | OWNER_PAY | TAX_EXEMPT | QUAL_DIV | LTCG_SPLIT | SEC1250 | K1_SPLIT | ...)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>YES — VBA auto-fills from Treatment_Profile_Map[Helper_Treatment]</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Rule for how Helper_Amount should be treated (e.g., QUAL_DIV → stack with LTCG).</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>K1_SPLIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Consider</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Text (free)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Free text — preparer note about the Consider_Prompt question</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Preparer's answer to whatever Consider_Prompt applies (e.g., "owner pay portion?" → "Yes, full $X is reasonable comp").</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Owner reasonable comp</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Text (free)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Free text</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any additional context.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Passive loss carried forward</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2298,7 +3209,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3076,7 +3987,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3710,7 +4621,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4272,7 +5183,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5490,7 +6401,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7170,13 +8081,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7236,6 +8147,21 @@
           <t>Activity_Type</t>
         </is>
       </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>TaxYears</t>
+        </is>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
+        <is>
+          <t>Helper_Treatments</t>
+        </is>
+      </c>
+      <c r="J3" s="13" t="inlineStr">
+        <is>
+          <t>Review_Status</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7273,6 +8199,19 @@
           <t>Baseline</t>
         </is>
       </c>
+      <c r="H4" t="n">
+        <v>2023</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7310,6 +8249,19 @@
           <t>Strategy</t>
         </is>
       </c>
+      <c r="H5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>OWNER_PAY</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7337,6 +8289,19 @@
           <t>2b</t>
         </is>
       </c>
+      <c r="H6" t="n">
+        <v>2025</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>TAX_EXEMPT</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7364,6 +8329,19 @@
           <t>3a</t>
         </is>
       </c>
+      <c r="H7" t="n">
+        <v>2026</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>QUAL_DIV</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Needs Rework</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7386,6 +8364,14 @@
           <t>3b</t>
         </is>
       </c>
+      <c r="H8" t="n">
+        <v>2027</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>LTCG_SPLIT</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7403,6 +8389,14 @@
           <t>7</t>
         </is>
       </c>
+      <c r="H9" t="n">
+        <v>2028</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>SEC1250</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7420,6 +8414,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>K1_SPLIT</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -7434,7 +8433,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ACTIVE_RE</t>
         </is>
       </c>
     </row>
@@ -7446,7 +8450,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>PASSIVE</t>
         </is>
       </c>
     </row>
@@ -7458,7 +8467,48 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>SE_INCOME</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>TRUST_DIST</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="F15" t="inlineStr">
+        <is>
           <t>13</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>HSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>IRA</t>
         </is>
       </c>
     </row>
@@ -7468,6 +8518,11 @@
           <t>▸ PER-BUCKET TREATMENT_PROFILE LISTS</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>RETIREMENT</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
@@ -7510,6 +8565,11 @@
           <t>Payment_Profiles</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>SE_HEALTH</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -7552,6 +8612,11 @@
           <t>Pmt_Withholding</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>STUDENT_LOAN</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -7594,6 +8659,11 @@
           <t>Pmt_EstTax</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -7626,6 +8696,11 @@
           <t>Cr_FTC</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>SALT</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -7653,6 +8728,11 @@
           <t>Itm_Charity</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>MORTGAGE</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -7670,6 +8750,11 @@
           <t>Adj_StudentLoan</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>CHARITY</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -7677,6 +8762,11 @@
           <t>K1_PTP_Passive</t>
         </is>
       </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>CTC</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -7684,11 +8774,21 @@
           <t>K1_SCorp_Active</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>EDUCATION</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
           <t>K1_SCorp_Passive</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>FTC</t>
         </is>
       </c>
     </row>
